--- a/COMPSYS704_Interface_V1_Integration_Test_Candidate_M4_V1_2_synced_fixed_28082026.xlsx
+++ b/COMPSYS704_Interface_V1_Integration_Test_Candidate_M4_V1_2_synced_fixed_28082026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6aa0aec50a884def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interfaces" sheetId="2" r:id="Rf5e30c0208fb4364"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ports" sheetId="3" r:id="Rdb6ac6c389674018"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payloads" sheetId="4" r:id="R9066946c32994f16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FT Details" sheetId="5" r:id="Rda8b99f5da9a4b12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Codes" sheetId="6" r:id="R08db47f54f8d4c3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Check" sheetId="8" r:id="R0aa048af29df4593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GP Hand-offs" sheetId="7" r:id="Rbdd8166178f54a91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M4 V1.2 Tests" sheetId="9" r:id="R617cf5d95d3f45d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R7fbdc9d762094d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interfaces" sheetId="2" r:id="R03c442c26e9641b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ports" sheetId="3" r:id="Rd1f20789ea5343c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payloads" sheetId="4" r:id="R76e727ef95704ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FT Details" sheetId="5" r:id="Rb24c449dd58449f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Codes" sheetId="6" r:id="R4ce7d6dc7cd44ab3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Check" sheetId="8" r:id="R1c5eb5588c414510"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GP Hand-offs" sheetId="7" r:id="Reb1f3df5af14438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M4 V1.2 Tests" sheetId="9" r:id="R6301d26cc7174117"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -75,18 +75,12 @@
     <x:t xml:space="preserve">Existing GP / POS / Visualisation</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Implemented at M1 ends; real peer Controllers remain external</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Explicit M3-facing V2.1 boundaries</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">FROZEN</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Mixed: M1 safety declarations/state/mapping implemented; M2/M3 peer work not owned by M1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">M2-owned receiver numbers</x:t>
   </x:si>
   <x:si>
@@ -354,18 +348,12 @@
     <x:t xml:space="preserve">Read-only request for current Lid status</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">M1 mapping matches target; peer source/XML absent</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">LID_STATUS</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Latest Lid status</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">M1 receiver implemented; peer source/XML absent</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">CapperControllerCD</x:t>
   </x:si>
   <x:si>
@@ -570,9 +558,6 @@
     <x:t xml:space="preserve">Emit once after required fill and sensor confirmation</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">NOT OWNED BY M1; peer implementation absent</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">GP hand-off P3</x:t>
   </x:si>
   <x:si>
@@ -591,9 +576,6 @@
     <x:t xml:space="preserve">M3 internal</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">NOT OWNED BY M1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">LID_CYCLE_DONE</x:t>
   </x:si>
   <x:si>
@@ -789,12 +771,6 @@
     <x:t xml:space="preserve">Transfer the unchanged full BottleContext after verified labelled-bottle removal to M4 size-aware sorting and carton packing</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">M4 V1.2 PROPOSED; M4 PORT ASSIGNED</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 approves full-context payload and sender rule; M4 implementation/team freeze pending</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Does not replace BOTTLE_DONE</x:t>
   </x:si>
   <x:si>
@@ -1071,429 +1047,390 @@
     <x:t xml:space="preserve">Provide validated bottle identity, size, capacity, geometry and packaging profile before admission</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">No competing registry</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UNLOAD_PROFILE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Provide the unchanged context for the matching bottle before downstream SortPack hand-off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Current Master Receiver Ports and V2.1 Transition</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Component / Boundary</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Clock Domain</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Implementation / Constraint</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">POS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Implemented</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ABS Coordinator</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FROZEN V1 + V2.1 FT inputs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Implemented; one shared SimpleServer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bottle Loader Controller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M1 mapping implemented; peer absent</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Conveyor status receiver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3 Rotary Table Controller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RotaryTableControllerCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Filler A Controller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Filler B Controller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lid Loader Controller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Capper Controller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Advanced ABS Visualisation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Implemented; display-only</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bottle Unloader Controller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3 Rotary Table Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3 Lid Loader Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">LidLoaderPlantCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3 Fault Supervisor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Transfer Fault Adapter</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Receives TRANSFER_RECOVERY_REQUEST; implementation pending</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Labeller P6 receiver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Labeller moved from 11011 to avoid M4 Registry 11011 / SortPack 11012; implementation pending</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Not frozen by M3-facing V2.1; test mode only</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FaultManagementGUI boundary</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Transport/port not frozen by M3-facing V2.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Bottle Loader Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Receives LOAD_CMD; M2 implementation pending</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Conveyor Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Receives MOTOR_CMD; M2 implementation pending</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Labeller Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Labeller Plant moved from 12011 to avoid M4 RecognitionPlant 12011 / SortPackPlant 12012</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 Bottle Unloader Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Receives UNLOAD_CMD; M2 implementation pending</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Receives batch, workpiece and resource-twin updates/queries; final transport schema pending</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4 Sort/Pack dependency</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4 BottleContext Registry</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4 Recognition Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RecognitionPlantCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4 SortPack Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SortPackPlantCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4 Filler Plants</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FillerAPlantCD / FillerBPlantCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">12004 / 12005</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4 Capper Plant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CapperPlantCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Interface Payload Formats</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Family</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Payload / Signal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Canonical Format</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Example / Rule</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">POS V1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">orderId|productCount|product1;product2;product3;product4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PO001|2|P1,60,40,5;P2,30,70,3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Product</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">productId,liquidARatio,liquidBRatio,quantity</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">P1,60,40,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">orderId|COMPLETED|completionTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PO001|COMPLETED|4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GP V2.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">P1/P2/P3/P4/P6 bottle hand-offs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">String value = bottleId</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">B104; stale/duplicate/wrong-bottle events rejected</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3 FT V2.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2|eventId|sourceEpoch|subsystem|faultCode|severity|bottleId|stateVersion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2|F021|E07|TRANSFER|ARRIVAL_TIMEOUT|WARNING|B104|18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2|eventId|sourceEpoch|action|attempt|expectedStateVersion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2|F021|E07|RETRY_TRANSFER|1|18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FROZEN V2.1; M2 receiver 13002 assigned</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2|eventId|sourceEpoch|attempt|ack|reason|acceptedStateVersion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2|F021|E07|1|ACCEPTED|route_clear|18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2|eventId|sourceEpoch|attempt|outcome|safeEvidence|serviceEvidence|resultingStateVersion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2|F021|E07|1|SUCCESS|motor_off+occupancy_consistent|arrival_confirmed|19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M1 safety messages</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Exact String field order is NOT DEFINED by supplied V2.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Signals/semantics are frozen; do not invent an incompatible parser</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SCHEMA GAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2.1 Field and Identity Rules</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Field</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rule</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">eventId</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Unique and stable for the event/recovery lifecycle</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sourceEpoch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Publisher boot/session ID; new registered epoch invalidates older in-flight events</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">stateVersion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Monotonic Controller-owned recovery-state version within one sourceEpoch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">attempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Supervisor-owned physical attempt number; attempt 1 is the maximum</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bottleId</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Required when known; use '-' when unavailable; never infer an identity</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Independent safe/service observation; failed sensor cannot verify itself</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">V2.1 Parsing / Idempotency</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Condition</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Receiver behaviour</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Duplicate eventId + attempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Return previous ACK/result; never repeat physical work</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Inactive sourceEpoch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reject STALE_EPOCH; no action</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lower stateVersion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reject STALE_STATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Unexpected higher stateVersion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Do not execute; request fresh state snapshot</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ACK timeout</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fail request; do not silently resend physical attempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Result timeout / invalid evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Report FT_RECOVERY_FAILED</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Legacy proposal payloads</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SUPERSEDED</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FaultEventV1 / RecoveryRequestV1 / RecoveryResultV1 / CoordinatorDecisionV1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Retained only in Markdown migration history</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Not current for explicitly superseded M3-facing V2.1 boundaries</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 GP</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">B104; internal permission only after label verification; does not clear P6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2 → M4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bottleId|sizeCode|capacityMl|geometryProfileId|packagingProfileId</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">B105|L|500|GEOM_L|PACK_L; M2 preserves unchanged; SortPack receiver 11012</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">M4 V1.2 PROPOSED; M2 APPROVES</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">M2 accepts only valid S/L mapping and preserves the context unchanged; implementation pending</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No competing registry</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNLOAD_PROFILE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Provide the unchanged context for the matching bottle before downstream SortPack hand-off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 latches only matching bottleId and forwards unchanged; implementation pending</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Current Master Receiver Ports and V2.1 Transition</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Component / Boundary</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Clock Domain</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Implementation / Constraint</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">POS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Implemented</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ABS Coordinator</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FROZEN V1 + V2.1 FT inputs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Implemented; one shared SimpleServer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bottle Loader Controller</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M1 mapping implemented; peer absent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Conveyor status receiver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3 Rotary Table Controller</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RotaryTableControllerCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Filler A Controller</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Filler B Controller</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lid Loader Controller</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M1 mapping matches target; peer absent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Capper Controller</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Advanced ABS Visualisation</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Implemented; display-only</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bottle Unloader Controller</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3 Rotary Table Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NOT OWNED BY M1; peer source/XML absent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3 Lid Loader Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LidLoaderPlantCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3 Fault Supervisor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M1 outputs mapped; M3 peer source/XML absent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Transfer Fault Adapter</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Receives TRANSFER_RECOVERY_REQUEST; implementation pending</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Labeller P6 receiver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Labeller moved from 11011 to avoid M4 Registry 11011 / SortPack 11012; implementation pending</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Not frozen by M3-facing V2.1; test mode only</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FaultManagementGUI boundary</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Transport/port not frozen by M3-facing V2.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Bottle Loader Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Receives LOAD_CMD; M2 implementation pending</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Conveyor Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Receives MOTOR_CMD; M2 implementation pending</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Labeller Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Labeller Plant moved from 12011 to avoid M4 RecognitionPlant 12011 / SortPackPlant 12012</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 Bottle Unloader Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Receives UNLOAD_CMD; M2 implementation pending</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Receives batch, workpiece and resource-twin updates/queries; final transport schema pending</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 Sort/Pack dependency</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 V1.2 PORT ASSIGNED / TEAM FREEZE PENDING</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Receives unchanged full-context BOTTLE_READY_FOR_SORT; M2 approves payload</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 BottleContext Registry</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 V1.2 ASSIGNED / PROPOSED</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Receives BOTTLE_RECOGNISED; no M2 binding</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 Recognition Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RecognitionPlantCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4-owned source Plant; no M2 binding</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 SortPack Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SortPackPlantCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4-owned Plant receiver; no M2 binding</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 Filler Plants</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FillerAPlantCD / FillerBPlantCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">12004 / 12005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4-owned Plant receivers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 Capper Plant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CapperPlantCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4-owned Plant receiver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Interface Payload Formats</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Family</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Payload / Signal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Canonical Format</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Example / Rule</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">POS V1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">orderId|productCount|product1;product2;product3;product4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PO001|2|P1,60,40,5;P2,30,70,3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Product</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">productId,liquidARatio,liquidBRatio,quantity</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">P1,60,40,5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">orderId|COMPLETED|completionTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PO001|COMPLETED|4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GP V2.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">P1/P2/P3/P4/P6 bottle hand-offs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">String value = bottleId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">B104; stale/duplicate/wrong-bottle events rejected</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3 FT V2.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2|eventId|sourceEpoch|subsystem|faultCode|severity|bottleId|stateVersion</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2|F021|E07|TRANSFER|ARRIVAL_TIMEOUT|WARNING|B104|18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2|eventId|sourceEpoch|action|attempt|expectedStateVersion</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2|F021|E07|RETRY_TRANSFER|1|18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FROZEN V2.1; M2 receiver 13002 assigned</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2|eventId|sourceEpoch|attempt|ack|reason|acceptedStateVersion</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2|F021|E07|1|ACCEPTED|route_clear|18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2|eventId|sourceEpoch|attempt|outcome|safeEvidence|serviceEvidence|resultingStateVersion</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2|F021|E07|1|SUCCESS|motor_off+occupancy_consistent|arrival_confirmed|19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M1 safety messages</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Exact String field order is NOT DEFINED by supplied V2.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Signals/semantics are frozen; do not invent an incompatible parser</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SCHEMA GAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2.1 Field and Identity Rules</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Field</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rule</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">eventId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unique and stable for the event/recovery lifecycle</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sourceEpoch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Publisher boot/session ID; new registered epoch invalidates older in-flight events</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">stateVersion</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Monotonic Controller-owned recovery-state version within one sourceEpoch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">attempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Supervisor-owned physical attempt number; attempt 1 is the maximum</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bottleId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Required when known; use '-' when unavailable; never infer an identity</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Independent safe/service observation; failed sensor cannot verify itself</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V2.1 Parsing / Idempotency</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Condition</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Receiver behaviour</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Duplicate eventId + attempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Return previous ACK/result; never repeat physical work</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Inactive sourceEpoch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reject STALE_EPOCH; no action</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lower stateVersion</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reject STALE_STATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unexpected higher stateVersion</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Do not execute; request fresh state snapshot</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ACK timeout</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fail request; do not silently resend physical attempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Result timeout / invalid evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Report FT_RECOVERY_FAILED</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Legacy proposal payloads</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SUPERSEDED</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FaultEventV1 / RecoveryRequestV1 / RecoveryResultV1 / CoordinatorDecisionV1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Retained only in Markdown migration history</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Not current for explicitly superseded M3-facing V2.1 boundaries</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 GP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">B104; internal permission only after label verification; does not clear P6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2 → M4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bottleId|sizeCode|capacityMl|geometryProfileId|packagingProfileId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">B105|L|500|GEOM_L|PACK_L; M2 preserves unchanged; SortPack receiver 11012</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Plant commands</x:t>
   </x:si>
   <x:si>
@@ -1545,9 +1482,6 @@
     <x:t xml:space="preserve">Only S|200|GEOM_S|PACK_S or L|500|GEOM_L|PACK_L</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">M4 PROPOSED; M2 APPROVES</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">LOAD_PROFILE / UNLOAD_PROFILE</x:t>
   </x:si>
   <x:si>
@@ -1593,9 +1527,6 @@
     <x:t xml:space="preserve">FaultSupervisorCD:13003</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Peer source/XML absent</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">M3</x:t>
   </x:si>
   <x:si>
@@ -1944,15 +1875,6 @@
     <x:t xml:space="preserve">M4 V1.2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">PASS — no M2 binding</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4/team freeze and XML verification</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PASS — concrete M2 hand-off receiver</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">PASS — moved from M4 12011/12012</x:t>
   </x:si>
   <x:si>
@@ -1977,9 +1899,6 @@
     <x:t xml:space="preserve">PASS — frozen receiver</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">M3 implementation / end-to-end test</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">M2 IP</x:t>
   </x:si>
   <x:si>
@@ -1998,21 +1917,9 @@
     <x:t xml:space="preserve">M4 V1.2 + M2 V1.0</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">PAYLOAD ALIGNED</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Team freeze; implement validation and unchanged forwarding</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">M2 -&gt; M4</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">PAYLOAD ALIGNED — full BottleContext</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Team freeze and integration test</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">LABELLER_STATUS_REQUEST / STATUS</x:t>
   </x:si>
   <x:si>
@@ -2049,18 +1956,12 @@
     <x:t xml:space="preserve">Once after required fill and sensor confirmation</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">FROZEN; M4/M3 — NOT OWNED BY M1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">P3</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Current filled P3 bottle only</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">FROZEN; M3 — NOT OWNED BY M1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">After placement sensor confirmation</x:t>
   </x:si>
   <x:si>
@@ -2110,9 +2011,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">After verified labelled-bottle removal; preserve full context; does not replace BOTTLE_DONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4 V1.2 proposed; M2 approves; team freeze/implementation pending</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3065,7 +2963,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="25" t="str">
-        <x:v>M1 production XML is aligned to ConveyorControllerCD:11009 and RotaryTableControllerCD:11003. Real M2/M3 Controller source/XML is unavailable, so peer implementation remains unverifiable. Proposed Labeller monitoring and M3 approval of M4 bottle-context hand-offs remain open.</x:v>
+        <x:v>M1, M3 and M4 production source/XML is present and structurally validated. Remaining external blockers are M2 Loader/Conveyor/Labeller/Unloader/Transfer Adapter endpoints and the full M2-to-M4 downstream hand-off.</x:v>
       </x:c>
       <x:c r="C8" s="1"/>
       <x:c r="D8" s="1"/>
@@ -3089,7 +2987,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="28" t="str">
-        <x:v>M2 V1.0 + M3 V2.1 + M4 V1.2 cross-checked 28 August 2026; M1 Conveyor/Rotary mapping and recipe-pair validation are aligned. Proposed Labeller monitoring and peer implementation/payload approvals remain open.</x:v>
+        <x:v>M2 V1.0 + M3 V2.1 + M4 V1.2 rechecked 2 September 2026. M1/M3/M4 production mappings are registered; M4 two-size implementation and tests pass; unresolved receiver warnings are M2-owned.</x:v>
       </x:c>
       <x:c r="C10" s="1"/>
       <x:c r="D10" s="1"/>
@@ -3127,8 +3025,8 @@
       <x:c r="B13" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>19</x:v>
+      <x:c r="C13" s="1" t="str">
+        <x:v>Implemented at M1, M3 and M4 ends; M2 peer Controllers remain external</x:v>
       </x:c>
       <x:c r="D13" s="1"/>
       <x:c r="E13" s="1"/>
@@ -3136,13 +3034,13 @@
     </x:row>
     <x:row r="14" ht="26">
       <x:c r="A14" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>22</x:v>
+      <x:c r="C14" s="1" t="str">
+        <x:v>M3 production Rotary/Lid/Fault Supervisor source, XML and self-tests are present; M2 Transfer peer remains pending</x:v>
       </x:c>
       <x:c r="D14" s="1"/>
       <x:c r="E14" s="1"/>
@@ -3150,13 +3048,13 @@
     </x:row>
     <x:row r="15" ht="26">
       <x:c r="A15" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="D15" s="1"/>
       <x:c r="E15" s="1"/>
@@ -3164,13 +3062,13 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="D16" s="1"/>
       <x:c r="E16" s="1"/>
@@ -3178,13 +3076,13 @@
     </x:row>
     <x:row r="17" ht="26">
       <x:c r="A17" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="12" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="B17" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="12" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="D17" s="1"/>
       <x:c r="E17" s="1"/>
@@ -3192,7 +3090,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="20" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B18" s="20"/>
       <x:c r="C18" s="20"/>
@@ -3202,10 +3100,10 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C19" s="1"/>
       <x:c r="D19" s="1"/>
@@ -3214,10 +3112,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C20" s="1"/>
       <x:c r="D20" s="1"/>
@@ -3226,10 +3124,10 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C21" s="1"/>
       <x:c r="D21" s="1"/>
@@ -3238,10 +3136,10 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1"/>
       <x:c r="D22" s="1"/>
@@ -3250,10 +3148,10 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1"/>
       <x:c r="D23" s="1"/>
@@ -3262,10 +3160,10 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1"/>
       <x:c r="D24" s="1"/>
@@ -3274,10 +3172,10 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C25" s="1"/>
       <x:c r="D25" s="1"/>
@@ -3286,10 +3184,10 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C26" s="1"/>
       <x:c r="D26" s="1"/>
@@ -3301,7 +3199,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C27" s="1"/>
       <x:c r="D27" s="1"/>
@@ -3310,18 +3208,18 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B29" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
@@ -3375,7 +3273,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B34" s="36" t="str">
-        <x:v>M1 status polling now targets RotaryTableControllerCD:11003. ROTARY_BOTTLE_CONTEXT is an M4-to-M3 proposed payload and still requires M3 payload/implementation approval; it is not an M1 Coordinator signal.</x:v>
+        <x:v>ROTARY_BOTTLE_CONTEXT, BOTTLE_AT_FILL and BOTTLE_AT_CAP are implemented at the M4 and M3 endpoints using the unchanged full BottleContext; they are machine-to-machine signals, not M1 Coordinator signals.</x:v>
       </x:c>
       <x:c r="C34" s="36"/>
       <x:c r="D34" s="36"/>
@@ -3434,60 +3332,60 @@
   <x:sheetData>
     <x:row r="1" ht="14" customHeight="1">
       <x:c r="A1" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="s">
+      <x:c r="D1" s="3" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="s">
+      <x:c r="E1" s="3" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="s">
+      <x:c r="F1" s="3" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="s">
+      <x:c r="G1" s="3" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="s">
+      <x:c r="H1" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="J1" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K1" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="D2" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="E2" s="1" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
         <x:v>Purchase-order payload. POS may transmit the same validated payload as up to three bounded PRESENT transport copies; Coordinator accepts one copy and does not restart an active or already-completed order ID.</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H2" s="1">
         <x:v>11001</x:v>
@@ -3496,31 +3394,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K2" s="1"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="C3" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="F3" s="1" t="str">
         <x:v>Completion payload. Coordinator may transmit the same payload as up to three bounded PRESENT transport copies; POS de-duplicates repeats and ignores stale/non-active completions.</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H3" s="1">
         <x:v>11000</x:v>
@@ -3529,31 +3427,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K3" s="1"/>
     </x:row>
     <x:row r="4" ht="14" customHeight="1">
       <x:c r="A4" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="E4" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="F4" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H4" s="1">
         <x:v>11002</x:v>
@@ -3562,31 +3460,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K4" s="1"/>
     </x:row>
     <x:row r="5" ht="14" customHeight="1">
       <x:c r="A5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H5" s="1">
         <x:v>11002</x:v>
@@ -3595,33 +3493,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K5" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="14" customHeight="1">
       <x:c r="A6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H6" s="1">
         <x:v>11001</x:v>
@@ -3630,99 +3528,99 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K6" s="1"/>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C7" s="12" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E7" s="12" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F7" s="12" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="G7" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H7" s="12">
         <x:v>11009</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J7" s="12" t="str">
         <x:v>M1 production XML targets ConveyorControllerCD:11009; M2 peer SystemJ/XML implementation remains unavailable.</x:v>
       </x:c>
       <x:c r="K7" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="14" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B8" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C8" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D8" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E8" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F8" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G8" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H8" s="12">
         <x:v>11001</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J8" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K8" s="12"/>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B9" s="27" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C9" s="27" t="str">
         <x:v>RotaryTableControllerCD</x:v>
       </x:c>
       <x:c r="D9" s="27" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E9" s="27" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F9" s="27" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G9" s="27" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H9" s="27" t="n">
         <x:v>11003</x:v>
@@ -3731,33 +3629,33 @@
         <x:v>FROZEN V2.1; M1 MAPPING ALIGNED</x:v>
       </x:c>
       <x:c r="J9" s="27" t="str">
-        <x:v>M1 production XML targets the frozen M3 receiver RotaryTableControllerCD:11003; peer SystemJ/XML remains unavailable.</x:v>
+        <x:v>M1 sender and M3 RotaryTableControllerCD:11003 receiver are implemented and aligned.</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B10" s="27" t="str">
         <x:v>RotaryTableControllerCD</x:v>
       </x:c>
       <x:c r="C10" s="27" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D10" s="27" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E10" s="27" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F10" s="27" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G10" s="27" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H10" s="27">
         <x:v>11001</x:v>
@@ -3766,25 +3664,25 @@
         <x:v>FROZEN V2.1; M1 MAPPING ALIGNED</x:v>
       </x:c>
       <x:c r="J10" s="27" t="str">
-        <x:v>M1 receiver is implemented at CoordinatorCD:11001; M3 sender implementation remains unavailable.</x:v>
+        <x:v>M3 sender and M1 CoordinatorCD:11001 receiver are implemented.</x:v>
       </x:c>
       <x:c r="K10" s="1"/>
     </x:row>
     <x:row r="11" ht="14" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F11" s="1" t="str">
         <x:v>Liquid A percentage, 0-100; M1 confirms the dispatched A/B pair sums to 100 before dispatch</x:v>
@@ -3799,7 +3697,7 @@
         <x:v>FROZEN V1; M4 V1.2 TRUST BOUNDARY</x:v>
       </x:c>
       <x:c r="J11" s="1" t="str">
-        <x:v>CONFIRMED — current POS and Coordinator OrderV1 validation enforce both ratios in 0..100 and pair sum = 100 before dispatch; M4 validates local A input.</x:v>
+        <x:v>Implemented at M1 sender and M4 FillerAControllerCD receiver; M1 validates the 0..100 complementary recipe pair and M4 validates its local input.</x:v>
       </x:c>
       <x:c r="K11" s="1" t="str">
         <x:v>Recipe input only; never an actuator command</x:v>
@@ -3807,25 +3705,25 @@
     </x:row>
     <x:row r="12" ht="14" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H12" s="1">
         <x:v>11004</x:v>
@@ -3833,34 +3731,34 @@
       <x:c r="I12" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J12" s="1" t="s">
-        <x:v>77</x:v>
+      <x:c r="J12" s="1" t="str">
+        <x:v>Implemented at M1 sender and M4 receiver; polling is read-only.</x:v>
       </x:c>
       <x:c r="K12" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="14" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H13" s="1">
         <x:v>11001</x:v>
@@ -3868,26 +3766,26 @@
       <x:c r="I13" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J13" s="1" t="s">
-        <x:v>84</x:v>
+      <x:c r="J13" s="1" t="str">
+        <x:v>Implemented at M4 sender and M1 receiver.</x:v>
       </x:c>
       <x:c r="K13" s="1"/>
     </x:row>
     <x:row r="14" ht="14" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F14" s="1" t="str">
         <x:v>Liquid B percentage, 0-100; M1 confirms the dispatched A/B pair sums to 100 before dispatch</x:v>
@@ -3902,7 +3800,7 @@
         <x:v>FROZEN V1; M4 V1.2 TRUST BOUNDARY</x:v>
       </x:c>
       <x:c r="J14" s="1" t="str">
-        <x:v>CONFIRMED — current POS and Coordinator OrderV1 validation enforce both ratios in 0..100 and pair sum = 100 before dispatch; M4 validates local B input and measured-A complement.</x:v>
+        <x:v>Implemented at M1 sender and M4 FillerBControllerCD receiver; measured-A complement is checked before B dosing.</x:v>
       </x:c>
       <x:c r="K14" s="1" t="str">
         <x:v>Recipe input only; never an actuator command</x:v>
@@ -3910,25 +3808,25 @@
     </x:row>
     <x:row r="15" ht="14" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>105</x:v>
-      </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H15" s="1">
         <x:v>11005</x:v>
@@ -3936,34 +3834,34 @@
       <x:c r="I15" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J15" s="1" t="s">
-        <x:v>77</x:v>
+      <x:c r="J15" s="1" t="str">
+        <x:v>Implemented at M1 sender and M4 receiver; polling is read-only.</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="14" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H16" s="1">
         <x:v>11001</x:v>
@@ -3971,100 +3869,100 @@
       <x:c r="I16" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J16" s="1" t="s">
-        <x:v>84</x:v>
+      <x:c r="J16" s="1" t="str">
+        <x:v>Implemented at M4 sender and M1 receiver.</x:v>
       </x:c>
       <x:c r="K16" s="1"/>
     </x:row>
     <x:row r="17" ht="14" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H17" s="1">
         <x:v>11006</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="str">
+        <x:v>Implemented at M1 sender and M3 receiver; polling is read-only.</x:v>
       </x:c>
       <x:c r="K17" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="14" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
         <x:v>11001</x:v>
       </x:c>
       <x:c r="I18" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J18" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J18" s="1" t="str">
+        <x:v>Implemented at M3 sender and M1 receiver.</x:v>
       </x:c>
       <x:c r="K18" s="1"/>
     </x:row>
     <x:row r="19" ht="14" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H19" s="1">
         <x:v>11007</x:v>
@@ -4072,34 +3970,34 @@
       <x:c r="I19" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J19" s="1" t="s">
-        <x:v>77</x:v>
+      <x:c r="J19" s="1" t="str">
+        <x:v>Implemented at M1 sender and M4 receiver; polling is read-only.</x:v>
       </x:c>
       <x:c r="K19" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="14" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H20" s="1">
         <x:v>11001</x:v>
@@ -4107,32 +4005,32 @@
       <x:c r="I20" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J20" s="1" t="s">
-        <x:v>84</x:v>
+      <x:c r="J20" s="1" t="str">
+        <x:v>Implemented at M4 sender and M1 receiver.</x:v>
       </x:c>
       <x:c r="K20" s="1"/>
     </x:row>
     <x:row r="21" ht="14" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>11010</x:v>
@@ -4141,33 +4039,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="14" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>11001</x:v>
@@ -4176,31 +4074,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K22" s="1"/>
     </x:row>
     <x:row r="23" ht="14" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F23" s="1" t="str">
         <x:v>Exactly one logical finished-bottle event after verified removal. Hold the pure signal PRESENT for one bounded observable window, then provide an ABSENT gap before the next bottle event.</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H23" s="1">
         <x:v>11001</x:v>
@@ -4217,25 +4115,25 @@
     </x:row>
     <x:row r="24" ht="14" customHeight="1">
       <x:c r="A24" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B24" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D24" s="9" t="s">
-        <x:v>129</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E24" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F24" s="9" t="s">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G24" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H24" s="9">
         <x:v>11008</x:v>
@@ -4244,33 +4142,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K24" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="14" customHeight="1">
       <x:c r="A25" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B25" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D25" s="9" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E25" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F25" s="9" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G25" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H25" s="9">
         <x:v>11008</x:v>
@@ -4279,33 +4177,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J25" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K25" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="14" customHeight="1">
       <x:c r="A26" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C26" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D26" s="9" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E26" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F26" s="9" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G26" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H26" s="9">
         <x:v>11008</x:v>
@@ -4314,33 +4212,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K26" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="14" customHeight="1">
       <x:c r="A27" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C27" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D27" s="9" t="s">
-        <x:v>137</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E27" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F27" s="9" t="s">
-        <x:v>138</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G27" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H27" s="9">
         <x:v>11008</x:v>
@@ -4349,33 +4247,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K27" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="14" customHeight="1">
       <x:c r="A28" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B28" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C28" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D28" s="9" t="s">
-        <x:v>139</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E28" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F28" s="9" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G28" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H28" s="9">
         <x:v>11008</x:v>
@@ -4384,33 +4282,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K28" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="14" customHeight="1">
       <x:c r="A29" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B29" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C29" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D29" s="9" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E29" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F29" s="9" t="s">
-        <x:v>142</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G29" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H29" s="9">
         <x:v>11008</x:v>
@@ -4419,33 +4317,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J29" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K29" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="14" customHeight="1">
       <x:c r="A30" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B30" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C30" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D30" s="9" t="s">
-        <x:v>143</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E30" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F30" s="9" t="s">
-        <x:v>144</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G30" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H30" s="9">
         <x:v>11008</x:v>
@@ -4454,33 +4352,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J30" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K30" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="14" customHeight="1">
       <x:c r="A31" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B31" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C31" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D31" s="9" t="s">
-        <x:v>145</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E31" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F31" s="9" t="s">
-        <x:v>146</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G31" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H31" s="9">
         <x:v>11008</x:v>
@@ -4489,33 +4387,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J31" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K31" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="14" customHeight="1">
       <x:c r="A32" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B32" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C32" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D32" s="9" t="s">
-        <x:v>147</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E32" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F32" s="9" t="s">
-        <x:v>148</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G32" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H32" s="9">
         <x:v>11008</x:v>
@@ -4524,33 +4422,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J32" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K32" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="14" customHeight="1">
       <x:c r="A33" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B33" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C33" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D33" s="9" t="s">
-        <x:v>149</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E33" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F33" s="9" t="s">
-        <x:v>150</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G33" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H33" s="9">
         <x:v>11008</x:v>
@@ -4559,789 +4457,789 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J33" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K33" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="14" customHeight="1">
       <x:c r="A34" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B34" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C34" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E34" s="6" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D34" s="6" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="E34" s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F34" s="6" t="s">
-        <x:v>154</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G34" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H34" s="6">
         <x:v>11001</x:v>
       </x:c>
       <x:c r="I34" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J34" s="6" t="s">
-        <x:v>155</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K34" s="6" t="s">
-        <x:v>156</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
       <x:c r="A35" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B35" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C35" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="E35" s="6" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D35" s="6" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="E35" s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F35" s="6" t="s">
-        <x:v>158</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G35" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H35" s="6">
         <x:v>11001</x:v>
       </x:c>
       <x:c r="I35" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J35" s="6" t="s">
-        <x:v>159</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K35" s="6" t="s">
-        <x:v>160</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="14" customHeight="1">
       <x:c r="A36" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B36" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C36" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="E36" s="6" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D36" s="6" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="E36" s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F36" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G36" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H36" s="6">
         <x:v>11001</x:v>
       </x:c>
       <x:c r="I36" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J36" s="6" t="s">
-        <x:v>155</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K36" s="6" t="s">
-        <x:v>163</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="14" customHeight="1">
       <x:c r="A37" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B37" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C37" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="E37" s="6" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D37" s="6" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="E37" s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F37" s="6" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G37" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H37" s="6">
         <x:v>11001</x:v>
       </x:c>
       <x:c r="I37" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J37" s="6" t="s">
-        <x:v>155</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K37" s="6" t="s">
-        <x:v>163</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
       <x:c r="A38" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B38" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E38" s="6" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C38" s="6" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D38" s="6" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="E38" s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F38" s="6" t="s">
-        <x:v>167</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G38" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H38" s="6">
         <x:v>13003</x:v>
       </x:c>
       <x:c r="I38" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J38" s="6" t="s">
-        <x:v>168</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="K38" s="6" t="s">
-        <x:v>169</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
       <x:c r="A39" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B39" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="E39" s="6" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C39" s="6" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D39" s="6" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="E39" s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F39" s="6" t="s">
-        <x:v>171</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G39" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H39" s="6">
         <x:v>13003</x:v>
       </x:c>
       <x:c r="I39" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J39" s="6" t="s">
-        <x:v>172</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="K39" s="6" t="s">
-        <x:v>169</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="14" customHeight="1">
       <x:c r="A40" s="12" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="E40" s="12" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="B40" s="12" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C40" s="12" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D40" s="12" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="E40" s="12" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F40" s="12" t="s">
-        <x:v>177</x:v>
-      </x:c>
       <x:c r="G40" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H40" s="12">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
-        <x:v>178</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K40" s="12" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="14" customHeight="1">
       <x:c r="A41" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H41" s="1">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="I41" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J41" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J41" s="1" t="str">
+        <x:v>Implemented at M4 sender and M3 RotaryTablePlantCD receiver; bottle-correlated completion only after both liquids are verified.</x:v>
       </x:c>
       <x:c r="K41" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="14" customHeight="1">
       <x:c r="A42" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G42" s="1"/>
       <x:c r="H42" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="I42" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J42" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J42" s="1" t="str">
+        <x:v>Implemented within M3.</x:v>
       </x:c>
       <x:c r="K42" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="14" customHeight="1">
       <x:c r="A43" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="C43" s="1" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D43" s="1" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="G43" s="1"/>
       <x:c r="H43" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="I43" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J43" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J43" s="1" t="str">
+        <x:v>Implemented within M3.</x:v>
       </x:c>
       <x:c r="K43" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="14" customHeight="1">
       <x:c r="A44" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H44" s="1">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="I44" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J44" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J44" s="1" t="str">
+        <x:v>Implemented at M4 sender and M3 RotaryTablePlantCD receiver; bottle-correlated completion only after sensor-confirmed capping.</x:v>
       </x:c>
       <x:c r="K44" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="14" customHeight="1">
       <x:c r="A45" s="12" t="s">
-        <x:v>198</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C45" s="12" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>200</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
-        <x:v>201</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G45" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H45" s="12">
         <x:v>11013</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
-        <x:v>202</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="K45" s="12" t="s">
-        <x:v>203</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="14" customHeight="1">
       <x:c r="A46" s="12" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B46" s="12" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="C46" s="12" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D46" s="12" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="B46" s="12" t="s">
+      <x:c r="E46" s="12" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F46" s="12" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="C46" s="12" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D46" s="12" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="E46" s="12" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F46" s="12" t="s">
-        <x:v>205</x:v>
-      </x:c>
       <x:c r="G46" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H46" s="12">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K46" s="12" t="s">
-        <x:v>207</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="14" customHeight="1">
       <x:c r="A47" s="12" t="s">
-        <x:v>198</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C47" s="12" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>208</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G47" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H47" s="12">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K47" s="12" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="14" customHeight="1">
       <x:c r="A48" s="13" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B48" s="13" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C48" s="13" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D48" s="13" t="s">
-        <x:v>213</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E48" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F48" s="13" t="s">
-        <x:v>214</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G48" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H48" s="13">
         <x:v>13003</x:v>
       </x:c>
       <x:c r="I48" s="13" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J48" s="13" t="s">
-        <x:v>215</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="K48" s="13"/>
     </x:row>
     <x:row r="49" ht="24" customHeight="1">
       <x:c r="A49" s="13" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B49" s="13" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C49" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D49" s="13" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="E49" s="13" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F49" s="13" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="B49" s="13" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C49" s="13" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D49" s="13" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="E49" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F49" s="13" t="s">
-        <x:v>217</x:v>
-      </x:c>
       <x:c r="G49" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H49" s="13">
         <x:v>13002</x:v>
       </x:c>
       <x:c r="I49" s="13" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J49" s="13" t="s">
-        <x:v>218</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K49" s="13" t="s">
-        <x:v>219</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="14" customHeight="1">
       <x:c r="A50" s="13" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B50" s="13" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C50" s="13" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D50" s="13" t="s">
-        <x:v>220</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="E50" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F50" s="13" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G50" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H50" s="13">
         <x:v>13003</x:v>
       </x:c>
       <x:c r="I50" s="13" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J50" s="13" t="s">
-        <x:v>215</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="K50" s="13" t="s">
-        <x:v>222</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="14" customHeight="1">
       <x:c r="A51" s="13" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C51" s="13" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D51" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E51" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F51" s="13" t="s">
-        <x:v>224</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G51" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H51" s="13">
         <x:v>13003</x:v>
       </x:c>
       <x:c r="I51" s="13" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J51" s="13" t="s">
-        <x:v>215</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="K51" s="13" t="s">
-        <x:v>222</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="14" customHeight="1">
       <x:c r="A52" s="6" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B52" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C52" s="6" t="s">
-        <x:v>226</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D52" s="6" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E52" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F52" s="6" t="s">
-        <x:v>229</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G52" s="6"/>
       <x:c r="H52" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I52" s="6" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="J52" s="6" t="s">
-        <x:v>231</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K52" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="14" customHeight="1">
       <x:c r="A53" s="6" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B53" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C53" s="6" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="D53" s="6" t="s">
-        <x:v>232</x:v>
-      </x:c>
       <x:c r="E53" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F53" s="6" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G53" s="6"/>
       <x:c r="H53" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I53" s="6" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="J53" s="6" t="s">
-        <x:v>231</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K53" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="14" customHeight="1">
       <x:c r="A54" s="6" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B54" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C54" s="6" t="s">
-        <x:v>226</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D54" s="6" t="s">
-        <x:v>234</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E54" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F54" s="6" t="s">
-        <x:v>235</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G54" s="6"/>
       <x:c r="H54" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I54" s="6" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="J54" s="6" t="s">
-        <x:v>231</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K54" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="14" customHeight="1">
       <x:c r="A55" s="6" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B55" s="6" t="s">
-        <x:v>226</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C55" s="6" t="s">
-        <x:v>236</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D55" s="6" t="s">
-        <x:v>237</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E55" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F55" s="6" t="s">
-        <x:v>238</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G55" s="6"/>
       <x:c r="H55" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I55" s="6" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="J55" s="6" t="s">
-        <x:v>231</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K55" s="6" t="s">
-        <x:v>239</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="26">
       <x:c r="A56" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B56" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C56" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D56" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E56" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F56" s="14" t="s">
-        <x:v>241</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G56" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H56" s="14">
         <x:v>11013</x:v>
@@ -5353,30 +5251,30 @@
         <x:v>Not implemented in M1: M2 production SystemJ/XML and a frozen Coordinator-facing Labeller monitoring contract are unavailable.</x:v>
       </x:c>
       <x:c r="K56" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26">
       <x:c r="A57" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B57" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C57" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D57" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E57" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F57" s="14" t="s">
-        <x:v>243</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G57" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H57" s="14">
         <x:v>11001</x:v>
@@ -5388,30 +5286,30 @@
         <x:v>Not implemented in M1: proposed conceptual sender only; peer source/XML and team acceptance are required.</x:v>
       </x:c>
       <x:c r="K57" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="26">
       <x:c r="A58" s="14" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B58" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C58" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D58" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E58" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F58" s="14" t="s">
-        <x:v>246</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G58" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H58" s="14">
         <x:v>11008</x:v>
@@ -5423,380 +5321,380 @@
         <x:v>Not implemented: no approved Coordinator Labeller status source exists; current Advanced Visualisation remains on ten VIZ_* inputs.</x:v>
       </x:c>
       <x:c r="K58" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="26">
       <x:c r="A59" s="14" t="s">
-        <x:v>247</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B59" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C59" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D59" s="14" t="s">
-        <x:v>248</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E59" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F59" s="14" t="s">
-        <x:v>249</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G59" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H59" s="14">
         <x:v>11010</x:v>
       </x:c>
       <x:c r="I59" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J59" s="14" t="s">
-        <x:v>251</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="K59" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="26">
       <x:c r="A60" s="14" t="s">
-        <x:v>252</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B60" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C60" s="14" t="s">
-        <x:v>253</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D60" s="14" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E60" s="14" t="s">
-        <x:v>255</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F60" s="14" t="s">
-        <x:v>256</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G60" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H60" s="14">
         <x:v>11012</x:v>
       </x:c>
-      <x:c r="I60" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="J60" s="14" t="s">
-        <x:v>258</x:v>
+      <x:c r="I60" s="14" t="str">
+        <x:v>M4 V1.2 RECEIVER IMPLEMENTED; M2 PEER PENDING</x:v>
+      </x:c>
+      <x:c r="J60" s="14" t="str">
+        <x:v>M4 SortPack receiver/Plant path is implemented and tested; M2 Unloader sender and merged peer test remain pending.</x:v>
       </x:c>
       <x:c r="K60" s="14" t="s">
-        <x:v>259</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="26">
       <x:c r="A61" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B61" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C61" s="14" t="s">
-        <x:v>261</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D61" s="14" t="s">
-        <x:v>262</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E61" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F61" s="14" t="s">
-        <x:v>263</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G61" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H61" s="14">
         <x:v>12002</x:v>
       </x:c>
       <x:c r="I61" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J61" s="14" t="s">
-        <x:v>264</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K61" s="14" t="s">
-        <x:v>265</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B62" s="14" t="s">
-        <x:v>261</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C62" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D62" s="14" t="s">
-        <x:v>266</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="E62" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F62" s="14" t="s">
-        <x:v>267</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G62" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H62" s="14">
         <x:v>11002</x:v>
       </x:c>
       <x:c r="I62" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J62" s="14" t="s">
-        <x:v>268</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="K62" s="14" t="s">
-        <x:v>269</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B63" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C63" s="14" t="s">
-        <x:v>270</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D63" s="14" t="s">
-        <x:v>271</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E63" s="14" t="s">
-        <x:v>272</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F63" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G63" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H63" s="14">
         <x:v>12009</x:v>
       </x:c>
       <x:c r="I63" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J63" s="14" t="s">
-        <x:v>264</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K63" s="14" t="s">
-        <x:v>274</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="26">
       <x:c r="A64" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B64" s="14" t="s">
-        <x:v>270</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C64" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D64" s="14" t="s">
-        <x:v>275</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E64" s="14" t="s">
-        <x:v>276</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="F64" s="14" t="s">
-        <x:v>277</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G64" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H64" s="14">
         <x:v>11009</x:v>
       </x:c>
       <x:c r="I64" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J64" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="K64" s="14" t="s">
-        <x:v>279</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="26">
       <x:c r="A65" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B65" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C65" s="14" t="s">
-        <x:v>280</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D65" s="14" t="s">
-        <x:v>281</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E65" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="F65" s="14" t="s">
-        <x:v>283</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="G65" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H65" s="14">
         <x:v>12013</x:v>
       </x:c>
       <x:c r="I65" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J65" s="14" t="s">
-        <x:v>284</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="K65" s="14" t="s">
-        <x:v>265</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="26">
       <x:c r="A66" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B66" s="14" t="s">
-        <x:v>280</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C66" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D66" s="14" t="s">
-        <x:v>285</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E66" s="14" t="s">
-        <x:v>286</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F66" s="14" t="s">
-        <x:v>287</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="G66" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H66" s="14">
         <x:v>11013</x:v>
       </x:c>
       <x:c r="I66" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J66" s="14" t="s">
-        <x:v>288</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K66" s="14" t="s">
-        <x:v>289</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B67" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C67" s="14" t="s">
-        <x:v>290</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D67" s="14" t="s">
-        <x:v>291</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E67" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F67" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G67" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H67" s="14">
         <x:v>12010</x:v>
       </x:c>
       <x:c r="I67" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J67" s="14" t="s">
-        <x:v>264</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K67" s="14" t="s">
-        <x:v>265</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="26">
       <x:c r="A68" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B68" s="14" t="s">
-        <x:v>290</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C68" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D68" s="14" t="s">
-        <x:v>293</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="E68" s="14" t="s">
-        <x:v>294</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="F68" s="14" t="s">
-        <x:v>295</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="G68" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H68" s="14">
         <x:v>11010</x:v>
       </x:c>
       <x:c r="I68" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J68" s="14" t="s">
-        <x:v>268</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="K68" s="14" t="s">
-        <x:v>296</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="26">
       <x:c r="A69" s="14" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B69" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C69" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D69" s="14" t="s">
-        <x:v>299</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E69" s="14" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F69" s="14" t="s">
-        <x:v>301</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G69" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H69" s="14">
         <x:v>14002</x:v>
@@ -5808,322 +5706,322 @@
         <x:v>No frozen payload/transport or M2 implementation is available; do not add this IP-only output to M1 yet.</x:v>
       </x:c>
       <x:c r="K69" s="14" t="s">
-        <x:v>302</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="26">
       <x:c r="A70" s="14" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="E70" s="14" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="B70" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="C70" s="14" t="s">
+      <x:c r="F70" s="14" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="D70" s="14" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="E70" s="14" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="F70" s="14" t="s">
-        <x:v>306</x:v>
-      </x:c>
       <x:c r="G70" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H70" s="14">
         <x:v>14002</x:v>
       </x:c>
       <x:c r="I70" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J70" s="14" t="s">
-        <x:v>307</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="K70" s="14" t="s">
-        <x:v>308</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="39">
       <x:c r="A71" s="14" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B71" s="14" t="s">
-        <x:v>309</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C71" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D71" s="14" t="s">
-        <x:v>310</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="E71" s="14" t="s">
-        <x:v>311</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F71" s="14" t="s">
-        <x:v>312</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="G71" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H71" s="14">
         <x:v>14002</x:v>
       </x:c>
       <x:c r="I71" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J71" s="14" t="s">
-        <x:v>313</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="K71" s="14" t="s">
-        <x:v>314</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="39">
       <x:c r="A72" s="14" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B72" s="14" t="s">
-        <x:v>315</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C72" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D72" s="14" t="s">
-        <x:v>316</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E72" s="14" t="s">
-        <x:v>317</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F72" s="14" t="s">
-        <x:v>318</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="G72" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H72" s="14">
         <x:v>14002</x:v>
       </x:c>
       <x:c r="I72" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J72" s="14" t="s">
-        <x:v>319</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="K72" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="26">
       <x:c r="A73" s="14" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B73" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C73" s="14" t="s">
-        <x:v>321</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D73" s="14" t="s">
-        <x:v>322</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E73" s="14" t="s">
-        <x:v>323</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F73" s="14" t="s">
-        <x:v>324</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="G73" s="14" t="s">
-        <x:v>325</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="H73" s="14" t="s">
-        <x:v>325</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="I73" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J73" s="14" t="s">
-        <x:v>326</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="K73" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="26">
       <x:c r="A74" s="14" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B74" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C74" s="14" t="s">
-        <x:v>327</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="D74" s="14" t="s">
-        <x:v>328</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E74" s="14" t="s">
-        <x:v>329</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F74" s="14" t="s">
-        <x:v>330</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="G74" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H74" s="14" t="s">
-        <x:v>331</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="I74" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J74" s="14" t="s">
-        <x:v>332</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="K74" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="26">
       <x:c r="A75" s="14" t="s">
-        <x:v>333</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B75" s="14" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C75" s="14" t="s">
-        <x:v>334</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="D75" s="14" t="s">
-        <x:v>335</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E75" s="14" t="s">
-        <x:v>336</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F75" s="14" t="s">
-        <x:v>337</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="G75" s="14" t="s">
-        <x:v>338</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="H75" s="14" t="s">
-        <x:v>338</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="I75" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J75" s="14" t="s">
-        <x:v>339</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="K75" s="14" t="s">
-        <x:v>340</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="26">
       <x:c r="A76" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="B76" s="14" t="s">
+      <x:c r="E76" s="14" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="C76" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D76" s="14" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="E76" s="14" t="s">
-        <x:v>342</x:v>
-      </x:c>
       <x:c r="F76" s="14" t="s">
-        <x:v>343</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="G76" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="H76" s="14" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="I76" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="J76" s="14" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="K76" s="14" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="H76" s="14" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="I76" s="14" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="J76" s="14" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="K76" s="14" t="s">
-        <x:v>346</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="26">
       <x:c r="A77" s="16" t="s">
-        <x:v>347</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B77" s="16" t="s">
-        <x:v>348</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C77" s="16" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D77" s="16" t="s">
-        <x:v>349</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="E77" s="16" t="s">
-        <x:v>255</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F77" s="16" t="s">
-        <x:v>350</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="G77" s="16" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H77" s="16">
         <x:v>11002</x:v>
       </x:c>
-      <x:c r="I77" s="16" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="J77" s="16" t="s">
-        <x:v>352</x:v>
+      <x:c r="I77" s="16" t="str">
+        <x:v>M4 V1.2 SENDER IMPLEMENTED; M2 PEER PENDING</x:v>
+      </x:c>
+      <x:c r="J77" s="16" t="str">
+        <x:v>M4 Registry sender validates and transmits the full context; M2 Loader receiver remains pending.</x:v>
       </x:c>
       <x:c r="K77" s="16" t="s">
-        <x:v>353</x:v>
+        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="26">
       <x:c r="A78" s="16" t="s">
-        <x:v>347</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B78" s="16" t="s">
-        <x:v>348</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C78" s="16" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D78" s="16" t="s">
-        <x:v>354</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="E78" s="16" t="s">
-        <x:v>255</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F78" s="16" t="s">
-        <x:v>355</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="G78" s="16" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H78" s="16">
         <x:v>11010</x:v>
       </x:c>
-      <x:c r="I78" s="16" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="J78" s="16" t="s">
-        <x:v>356</x:v>
+      <x:c r="I78" s="16" t="str">
+        <x:v>M4 V1.2 SENDER IMPLEMENTED; M2 PEER PENDING</x:v>
+      </x:c>
+      <x:c r="J78" s="16" t="str">
+        <x:v>M4 Registry sender validates and transmits the full context; M2 Unloader receiver remains pending.</x:v>
       </x:c>
       <x:c r="K78" s="16" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="46" customHeight="1">
@@ -6152,10 +6050,10 @@
         <x:v>11011</x:v>
       </x:c>
       <x:c r="I79" s="38" t="str">
-        <x:v>M4 V1.2 PROPOSED</x:v>
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
       </x:c>
       <x:c r="J79" s="38" t="str">
-        <x:v>M4-owned receiver; Recognition algorithm remains out of scope</x:v>
+        <x:v>RecognitionPlantCD and BottleContextRegistryCD endpoints are implemented; the real recognition algorithm remains out of scope.</x:v>
       </x:c>
       <x:c r="K79" s="38" t="str">
         <x:v>No actuator action on invalid context</x:v>
@@ -6187,10 +6085,10 @@
         <x:v>11003</x:v>
       </x:c>
       <x:c r="I80" s="38" t="str">
-        <x:v>M4 V1.2 PROPOSED; M3 APPROVAL REQUIRED</x:v>
+        <x:v>M4/M3 IMPLEMENTED</x:v>
       </x:c>
       <x:c r="J80" s="38" t="str">
-        <x:v>M1 status receiver mapping is aligned; this separate M4-to-M3 payload still requires M3 payload approval and peer implementation.</x:v>
+        <x:v>M4 Registry sender and M3 Rotary receiver use the unchanged full BottleContext.</x:v>
       </x:c>
       <x:c r="K80" s="38" t="str">
         <x:v>Not an M1 Coordinator signal</x:v>
@@ -6222,10 +6120,10 @@
         <x:v>11004</x:v>
       </x:c>
       <x:c r="I81" s="38" t="str">
-        <x:v>M4 V1.2 PROPOSED; M3 APPROVAL REQUIRED</x:v>
+        <x:v>M4/M3 IMPLEMENTED</x:v>
       </x:c>
       <x:c r="J81" s="38" t="str">
-        <x:v>Receiver is M4-owned; cross-team payload remains proposed</x:v>
+        <x:v>M3 same-bottle P2 relay and M4 Filler A receiver are implemented.</x:v>
       </x:c>
       <x:c r="K81" s="38" t="str">
         <x:v>Reject stale, duplicate, malformed or mismatched context</x:v>
@@ -6257,10 +6155,10 @@
         <x:v>11005</x:v>
       </x:c>
       <x:c r="I82" s="38" t="str">
-        <x:v>M4 V1.2 INTERNAL PROPOSED</x:v>
+        <x:v>M4 INTERNAL IMPLEMENTED</x:v>
       </x:c>
       <x:c r="J82" s="38" t="str">
-        <x:v>M4-owned hand-off; measuredAMl uses canonical unsigned integer mL</x:v>
+        <x:v>Implemented idempotent full-context plus measuredAMl hand-off; Filler B remains closed on mismatch.</x:v>
       </x:c>
       <x:c r="K82" s="38" t="str">
         <x:v>Filler B remains closed on mismatch</x:v>
@@ -6292,10 +6190,10 @@
         <x:v>12003</x:v>
       </x:c>
       <x:c r="I83" s="38" t="str">
-        <x:v>FROZEN BY M3 V2.1</x:v>
+        <x:v>FROZEN M3 V2.1; M4/M3 IMPLEMENTED</x:v>
       </x:c>
       <x:c r="J83" s="38" t="str">
-        <x:v>M4 sender implementation pending; M3 receiver retained</x:v>
+        <x:v>M4 sender and M3 Plant receiver are implemented; duplicate transport copies do not repeat physical work.</x:v>
       </x:c>
       <x:c r="K83" s="38" t="str">
         <x:v>Bottle correlated; never BOTTLE_DONE</x:v>
@@ -6327,10 +6225,10 @@
         <x:v>11007</x:v>
       </x:c>
       <x:c r="I84" s="38" t="str">
-        <x:v>M4 V1.2 PROPOSED; M3 APPROVAL REQUIRED</x:v>
+        <x:v>M4/M3 IMPLEMENTED</x:v>
       </x:c>
       <x:c r="J84" s="38" t="str">
-        <x:v>Receiver is M4-owned; cross-team payload remains proposed</x:v>
+        <x:v>M3 same-bottle P4 relay and M4 Capper receiver are implemented.</x:v>
       </x:c>
       <x:c r="K84" s="38" t="str">
         <x:v>Reject stale, duplicate, malformed or mismatched context</x:v>
@@ -6362,10 +6260,10 @@
         <x:v>12003</x:v>
       </x:c>
       <x:c r="I85" s="38" t="str">
-        <x:v>FROZEN BY M3 V2.1</x:v>
+        <x:v>FROZEN M3 V2.1; M4/M3 IMPLEMENTED</x:v>
       </x:c>
       <x:c r="J85" s="38" t="str">
-        <x:v>M4 sender implementation pending; M3 receiver retained</x:v>
+        <x:v>M4 sender and M3 Plant receiver are implemented; completion follows the full safe Capper sequence.</x:v>
       </x:c>
       <x:c r="K85" s="38" t="str">
         <x:v>Bottle correlated; never BOTTLE_DONE</x:v>
@@ -6397,10 +6295,10 @@
         <x:v>12012</x:v>
       </x:c>
       <x:c r="I86" s="38" t="str">
-        <x:v>M4 V1.2 PROPOSED</x:v>
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
       </x:c>
       <x:c r="J86" s="38" t="str">
-        <x:v>M4-owned Controller/Plant boundary; calibration and exact local encoding remain implementation details</x:v>
+        <x:v>M4 Controller/Plant lane selection, placement confirmation and package counting are implemented and tested.</x:v>
       </x:c>
       <x:c r="K86" s="38" t="str">
         <x:v>No count on wrong lane or missing package</x:v>
@@ -6417,7 +6315,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d5a0a2ca00a4140"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac0e558c35234b50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6436,7 +6334,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="19" t="s">
-        <x:v>357</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -6454,99 +6352,99 @@
     </x:row>
     <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>358</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>359</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>360</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="14" customHeight="1">
       <x:c r="A4" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>11000</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="14" customHeight="1">
       <x:c r="A5" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>11001</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="14" customHeight="1">
       <x:c r="A6" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>11002</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="14" customHeight="1">
       <x:c r="A7" s="11" t="s">
-        <x:v>368</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B7" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C7" s="11">
         <x:v>11009</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F7" s="25" t="str">
         <x:v>M1 production XML now targets ConveyorControllerCD:11009; peer implementation pending/unavailable.</x:v>
@@ -6554,10 +6452,10 @@
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="28" t="s">
-        <x:v>369</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B8" s="28" t="s">
-        <x:v>370</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C8" s="28" t="n">
         <x:v>11003</x:v>
@@ -6569,483 +6467,483 @@
         <x:v>FROZEN V2.1; M1 MAPPING ALIGNED</x:v>
       </x:c>
       <x:c r="F8" s="28" t="str">
-        <x:v>M1 production XML now targets RotaryTableControllerCD:11003; M3 peer source/XML is unavailable.</x:v>
+        <x:v>Implemented; M1 production XML and M3 receiver are aligned.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="14" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>11004</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>367</x:v>
+      <x:c r="F9" s="1" t="str">
+        <x:v>Implemented M4 Controller receiver; M1 mapping aligned.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="14" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>11005</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>367</x:v>
+      <x:c r="F10" s="1" t="str">
+        <x:v>Implemented M4 Controller receiver; M1 mapping aligned.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="14" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>11006</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="str">
+        <x:v>Implemented M3 Controller receiver; M1 mapping aligned.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="14" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>11007</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>367</x:v>
+      <x:c r="F12" s="1" t="str">
+        <x:v>Implemented M4 Controller receiver; M1 mapping aligned.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="14" customHeight="1">
       <x:c r="A13" s="9" t="s">
-        <x:v>376</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B13" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C13" s="9">
         <x:v>11008</x:v>
       </x:c>
       <x:c r="D13" s="9" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E13" s="9" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F13" s="9" t="s">
-        <x:v>377</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="14" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>11010</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="14" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="str">
+        <x:v>Implemented M3 Plant receiver; M4 MARK_FILLED/MARK_CAPPED mappings aligned.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="14" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>12006</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="str">
+        <x:v>Implemented M3 Plant receiver.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="14" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>383</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C17" s="6">
         <x:v>13003</x:v>
       </x:c>
       <x:c r="D17" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E17" s="6" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F17" s="6" t="s">
-        <x:v>384</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>Implemented M3 Fault Supervisor; M2 Transfer Adapter peer remains pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="14" customHeight="1">
       <x:c r="A18" s="11" t="s">
-        <x:v>385</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B18" s="11" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C18" s="11">
         <x:v>13002</x:v>
       </x:c>
       <x:c r="D18" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E18" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F18" s="11" t="s">
-        <x:v>386</x:v>
+        <x:v>372</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="14" customHeight="1">
       <x:c r="A19" s="11" t="s">
-        <x:v>387</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B19" s="11" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C19" s="11">
         <x:v>11013</x:v>
       </x:c>
       <x:c r="D19" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E19" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F19" s="11" t="s">
-        <x:v>388</x:v>
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="14" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>236</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B20" s="6" t="s">
-        <x:v>236</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C20" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D20" s="6"/>
       <x:c r="E20" s="6" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F20" s="6" t="s">
-        <x:v>389</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="14" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>390</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B21" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C21" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D21" s="6"/>
       <x:c r="E21" s="6" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F21" s="6" t="s">
-        <x:v>391</x:v>
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="s">
-        <x:v>392</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B22" s="11" t="s">
-        <x:v>261</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C22" s="11">
         <x:v>12002</x:v>
       </x:c>
       <x:c r="D22" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E22" s="11" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F22" s="11" t="s">
-        <x:v>393</x:v>
+        <x:v>379</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="s">
-        <x:v>394</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B23" s="11" t="s">
-        <x:v>270</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C23" s="11">
         <x:v>12009</x:v>
       </x:c>
       <x:c r="D23" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E23" s="11" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F23" s="11" t="s">
-        <x:v>395</x:v>
+        <x:v>381</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="s">
-        <x:v>396</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B24" s="11" t="s">
-        <x:v>280</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C24" s="11">
         <x:v>12013</x:v>
       </x:c>
       <x:c r="D24" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E24" s="11" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F24" s="11" t="s">
-        <x:v>397</x:v>
+        <x:v>383</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="s">
-        <x:v>398</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B25" s="11" t="s">
-        <x:v>290</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C25" s="11">
         <x:v>12010</x:v>
       </x:c>
       <x:c r="D25" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E25" s="11" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F25" s="11" t="s">
-        <x:v>399</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B26" s="11" t="s">
-        <x:v>298</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C26" s="11">
         <x:v>14002</x:v>
       </x:c>
       <x:c r="D26" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E26" s="11" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F26" s="11" t="s">
-        <x:v>400</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="26">
       <x:c r="A27" s="11" t="s">
-        <x:v>401</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B27" s="11" t="s">
-        <x:v>253</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C27" s="11">
         <x:v>11012</x:v>
       </x:c>
       <x:c r="D27" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="s">
-        <x:v>402</x:v>
-      </x:c>
-      <x:c r="F27" s="11" t="s">
-        <x:v>403</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>M4 V1.2 IMPLEMENTED; M2 PEER PENDING</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>M4 receiver and local SortPack path implemented; M2 BOTTLE_READY_FOR_SORT sender pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="s">
-        <x:v>404</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B28" s="11" t="s">
-        <x:v>348</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C28" s="11">
         <x:v>11011</x:v>
       </x:c>
       <x:c r="D28" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="s">
-        <x:v>406</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str">
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str">
+        <x:v>Implemented receiver for validated BOTTLE_RECOGNISED and full-context distribution.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="s">
-        <x:v>407</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B29" s="11" t="s">
-        <x:v>408</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C29" s="11">
         <x:v>12011</x:v>
       </x:c>
       <x:c r="D29" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="F29" s="11" t="s">
-        <x:v>409</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str">
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>Implemented M4 recognition source Plant; recognition algorithm remains conceptual/out of scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="s">
-        <x:v>410</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B30" s="11" t="s">
-        <x:v>411</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="C30" s="11">
         <x:v>12012</x:v>
       </x:c>
       <x:c r="D30" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="s">
-        <x:v>412</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str">
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="str">
+        <x:v>Implemented M4 SortPack Plant receiver.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="s">
-        <x:v>413</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B31" s="11" t="s">
-        <x:v>414</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C31" s="11" t="s">
-        <x:v>415</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="D31" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="s">
-        <x:v>416</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str">
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>Implemented M4 Filler A/B Plant receivers.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="s">
-        <x:v>417</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B32" s="11" t="s">
-        <x:v>418</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C32" s="11">
         <x:v>12007</x:v>
       </x:c>
       <x:c r="D32" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="F32" s="11" t="s">
-        <x:v>419</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str">
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>Implemented M4 Capper Plant receiver.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7069,7 +6967,7 @@
   <x:sheetData>
     <x:row r="1" ht="19.5">
       <x:c r="A1" s="19" t="s">
-        <x:v>420</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -7085,33 +6983,33 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="s">
-        <x:v>421</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>422</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>423</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>424</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>425</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>5</x:v>
@@ -7119,16 +7017,16 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>5</x:v>
@@ -7136,16 +7034,16 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>5</x:v>
@@ -7153,104 +7051,104 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="6" t="s">
-        <x:v>438</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>213</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>439</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
-        <x:v>440</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26">
       <x:c r="A9" s="13" t="s">
-        <x:v>438</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>216</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>441</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="D9" s="13" t="s">
-        <x:v>442</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E9" s="13" t="s">
-        <x:v>443</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="13" t="s">
-        <x:v>438</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>220</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C10" s="13" t="s">
-        <x:v>444</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="D10" s="13" t="s">
-        <x:v>445</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E10" s="13" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="13" t="s">
-        <x:v>438</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
-        <x:v>446</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="D11" s="13" t="s">
-        <x:v>447</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6" t="s">
-        <x:v>438</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>448</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>449</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="D12" s="6" t="s">
-        <x:v>450</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="E12" s="6" t="s">
-        <x:v>451</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7262,7 +7160,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="20" t="s">
-        <x:v>452</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B14" s="20"/>
       <x:c r="C14" s="20"/>
@@ -7271,10 +7169,10 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="C15" s="1"/>
       <x:c r="D15" s="1"/>
@@ -7282,10 +7180,10 @@
     </x:row>
     <x:row r="16" ht="26">
       <x:c r="A16" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C16" s="1"/>
       <x:c r="D16" s="1"/>
@@ -7293,10 +7191,10 @@
     </x:row>
     <x:row r="17" ht="26">
       <x:c r="A17" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C17" s="1"/>
       <x:c r="D17" s="1"/>
@@ -7304,10 +7202,10 @@
     </x:row>
     <x:row r="18" ht="26">
       <x:c r="A18" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="C18" s="1"/>
       <x:c r="D18" s="1"/>
@@ -7315,10 +7213,10 @@
     </x:row>
     <x:row r="19" ht="26">
       <x:c r="A19" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="C19" s="1"/>
       <x:c r="D19" s="1"/>
@@ -7326,10 +7224,10 @@
     </x:row>
     <x:row r="20" ht="26">
       <x:c r="A20" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="C20" s="1"/>
       <x:c r="D20" s="1"/>
@@ -7337,10 +7235,10 @@
     </x:row>
     <x:row r="21" ht="26">
       <x:c r="A21" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C21" s="1"/>
       <x:c r="D21" s="1"/>
@@ -7355,7 +7253,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="20" t="s">
-        <x:v>467</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B23" s="20"/>
       <x:c r="C23" s="20"/>
@@ -7364,10 +7262,10 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="3" t="s">
-        <x:v>468</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>469</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C24" s="1"/>
       <x:c r="D24" s="1"/>
@@ -7375,10 +7273,10 @@
     </x:row>
     <x:row r="25" ht="26">
       <x:c r="A25" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C25" s="1"/>
       <x:c r="D25" s="1"/>
@@ -7386,10 +7284,10 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C26" s="1"/>
       <x:c r="D26" s="1"/>
@@ -7397,10 +7295,10 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="C27" s="1"/>
       <x:c r="D27" s="1"/>
@@ -7408,10 +7306,10 @@
     </x:row>
     <x:row r="28" ht="26">
       <x:c r="A28" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C28" s="1"/>
       <x:c r="D28" s="1"/>
@@ -7419,10 +7317,10 @@
     </x:row>
     <x:row r="29" ht="26">
       <x:c r="A29" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C29" s="1"/>
       <x:c r="D29" s="1"/>
@@ -7430,10 +7328,10 @@
     </x:row>
     <x:row r="30" ht="26">
       <x:c r="A30" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C30" s="1"/>
       <x:c r="D30" s="1"/>
@@ -7448,7 +7346,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="20" t="s">
-        <x:v>482</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B32" s="20"/>
       <x:c r="C32" s="20"/>
@@ -7457,155 +7355,155 @@
     </x:row>
     <x:row r="33" ht="26">
       <x:c r="A33" s="8" t="s">
-        <x:v>483</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B33" s="8" t="s">
-        <x:v>484</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C33" s="8" t="s">
-        <x:v>485</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D33" s="8" t="s">
-        <x:v>486</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="E33" s="8" t="s">
-        <x:v>483</x:v>
+        <x:v>461</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="13" t="s">
-        <x:v>487</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B34" s="13" t="s">
-        <x:v>248</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C34" s="13" t="s">
-        <x:v>436</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D34" s="13" t="s">
-        <x:v>488</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E34" s="13" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="13" t="s">
-        <x:v>489</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C35" s="13" t="s">
-        <x:v>490</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D35" s="13" t="s">
-        <x:v>491</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E35" s="13" t="s">
-        <x:v>351</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="13" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>492</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="C36" s="13" t="s">
-        <x:v>493</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="D36" s="13" t="s">
-        <x:v>494</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="E36" s="13" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="13" t="s">
-        <x:v>260</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>495</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="C37" s="13" t="s">
-        <x:v>496</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="D37" s="13" t="s">
-        <x:v>497</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="E37" s="13" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="13" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>299</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C38" s="13" t="s">
-        <x:v>498</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="D38" s="13" t="s">
-        <x:v>499</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="E38" s="13" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="13" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B39" s="13" t="s">
-        <x:v>304</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C39" s="13" t="s">
-        <x:v>500</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D39" s="13" t="s">
-        <x:v>501</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E39" s="13" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="13" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>310</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C40" s="13" t="s">
-        <x:v>502</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D40" s="13" t="s">
-        <x:v>503</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="E40" s="13" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="13" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>504</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="C41" s="13" t="s">
-        <x:v>505</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="D41" s="13" t="s">
-        <x:v>506</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E41" s="13" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -7613,16 +7511,16 @@
         <x:v>Cross-team approval summary — M4/M2</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>507</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C42" s="13" t="s">
-        <x:v>490</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D42" s="13" t="s">
-        <x:v>508</x:v>
-      </x:c>
-      <x:c r="E42" s="13" t="s">
-        <x:v>509</x:v>
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="E42" s="13" t="str">
+        <x:v>M4 IMPLEMENTED; M2 PEER APPROVED/PENDING</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -7630,16 +7528,16 @@
         <x:v>Cross-team approval summary — M4 -&gt; M2</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>510</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="C43" s="13" t="s">
-        <x:v>507</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="D43" s="13" t="s">
-        <x:v>511</x:v>
-      </x:c>
-      <x:c r="E43" s="13" t="s">
-        <x:v>509</x:v>
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="E43" s="13" t="str">
+        <x:v>M4 SENDER IMPLEMENTED; M2 RECEIVERS PENDING</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -7647,16 +7545,16 @@
         <x:v>Cross-team approval summary — M2 -&gt; M4</x:v>
       </x:c>
       <x:c r="B44" s="13" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C44" s="13" t="s">
-        <x:v>507</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="D44" s="13" t="s">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="E44" s="13" t="s">
-        <x:v>509</x:v>
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="E44" s="13" t="str">
+        <x:v>M4 RECEIVER IMPLEMENTED; M2 SENDER PENDING</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="30" customHeight="1">
@@ -7710,7 +7608,7 @@
         <x:v>B104|S|200</x:v>
       </x:c>
       <x:c r="E48" s="48" t="str">
-        <x:v>M4 V1.2 PROPOSED</x:v>
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="42" customHeight="1">
@@ -7727,7 +7625,7 @@
         <x:v>B104|S|200|GEOM_S|PACK_S</x:v>
       </x:c>
       <x:c r="E49" s="48" t="str">
-        <x:v>M4 PROPOSED; M2 APPROVES</x:v>
+        <x:v>M4 IMPLEMENTED; M2 PEER PENDING</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
@@ -7741,10 +7639,10 @@
         <x:v>bottleId|sizeCode|capacityMl|geometryProfileId|packagingProfileId</x:v>
       </x:c>
       <x:c r="D50" s="48" t="str">
-        <x:v>Receiver RotaryTableControllerCD:11003; M3 payload approval and implementation still required</x:v>
+        <x:v>M4 Registry sender and M3 RotaryTableControllerCD:11003 receiver implemented.</x:v>
       </x:c>
       <x:c r="E50" s="48" t="str">
-        <x:v>M4 PROPOSED; M3 APPROVAL REQUIRED</x:v>
+        <x:v>M4/M3 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
@@ -7761,7 +7659,7 @@
         <x:v>B105|L|500|GEOM_L|PACK_L</x:v>
       </x:c>
       <x:c r="E51" s="48" t="str">
-        <x:v>M4 PROPOSED; M3 APPROVAL REQUIRED</x:v>
+        <x:v>M4/M3 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
@@ -7778,7 +7676,7 @@
         <x:v>B104|S|200|GEOM_S|PACK_S|120</x:v>
       </x:c>
       <x:c r="E52" s="48" t="str">
-        <x:v>M4 V1.2 INTERNAL PROPOSED</x:v>
+        <x:v>M4 INTERNAL IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
@@ -7795,7 +7693,7 @@
         <x:v>B104; receiver RotaryTablePlantCD:12003</x:v>
       </x:c>
       <x:c r="E53" s="48" t="str">
-        <x:v>FROZEN BY M3 V2.1</x:v>
+        <x:v>FROZEN M3 V2.1; M4/M3 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="42" customHeight="1">
@@ -7812,7 +7710,7 @@
         <x:v>B105|L|500|GEOM_L|PACK_L; preserve unchanged</x:v>
       </x:c>
       <x:c r="E54" s="48" t="str">
-        <x:v>M4 PROPOSED; M2 APPROVES</x:v>
+        <x:v>M4 RECEIVER IMPLEMENTED; M2 SENDER PENDING</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
@@ -7829,7 +7727,7 @@
         <x:v>ASCII pipe-delimited; no sign, decimal point or leading zero</x:v>
       </x:c>
       <x:c r="E55" s="48" t="str">
-        <x:v>M4 V1.2 PROPOSED</x:v>
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
@@ -7846,7 +7744,7 @@
         <x:v>No other size/capacity/profile combination is valid</x:v>
       </x:c>
       <x:c r="E56" s="48" t="str">
-        <x:v>M4 V1.2 PROPOSED</x:v>
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
@@ -7863,7 +7761,7 @@
         <x:v>Must satisfy target/tolerance and measuredAMl + targetB = capacityMl within tolerance</x:v>
       </x:c>
       <x:c r="E57" s="48" t="str">
-        <x:v>M4 V1.2 PROPOSED</x:v>
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="42" customHeight="1">
@@ -7880,7 +7778,7 @@
         <x:v>CONFIRMED in current M1 OrderV1 validation before Coordinator dispatch; M4 does not claim pre-dose visibility of both values</x:v>
       </x:c>
       <x:c r="E58" s="48" t="str">
-        <x:v>CONFIRMED IN CURRENT M1 IMPLEMENTATION</x:v>
+        <x:v>CONFIRMED M1/M4 IMPLEMENTATION</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="48" customHeight="1">
@@ -7897,7 +7795,7 @@
         <x:v>For S=200 and L=500 with Integer ratios, results are integral mL; no rounding is permitted</x:v>
       </x:c>
       <x:c r="E59" s="111" t="str">
-        <x:v>WORKBOOK CLARIFICATION — ADD TO NEXT M4 CONTRACT REVISION</x:v>
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="48" customHeight="1">
@@ -7914,7 +7812,7 @@
         <x:v>Preserve byte-for-byte through Recognition, Registry, M2, M3 and M4; reject malformed identity before physical action</x:v>
       </x:c>
       <x:c r="E60" s="111" t="str">
-        <x:v>WORKBOOK CLARIFICATION — ADD TO NEXT M4 CONTRACT REVISION</x:v>
+        <x:v>M4 V1.2 IMPLEMENTED</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7941,7 +7839,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="19" t="s">
-        <x:v>513</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -7949,7 +7847,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="21" t="s">
-        <x:v>514</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -7963,7 +7861,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
         <x:v>16</x:v>
@@ -7972,91 +7870,91 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>494</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="6" t="s">
-        <x:v>517</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>518</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>519</x:v>
+        <x:v>497</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26">
       <x:c r="A6" s="6" t="s">
-        <x:v>520</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
         <x:v>DECLARED/MAPPED via OptionalSimpleClient; NOT EMITTED</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>521</x:v>
+        <x:v>499</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="6" t="s">
-        <x:v>522</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C7" s="6" t="str">
         <x:v>DECLARED/MAPPED via OptionalSimpleClient; NOT EMITTED</x:v>
       </x:c>
       <x:c r="D7" s="6" t="s">
-        <x:v>523</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="6" t="s">
-        <x:v>524</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="s">
-        <x:v>525</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>IMPLEMENTED in M3 source/XML; M1 mappings aligned</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
-        <x:v>526</x:v>
+        <x:v>503</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="13" t="s">
-        <x:v>385</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>527</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>528</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D9" s="13" t="s">
-        <x:v>529</x:v>
+        <x:v>506</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="6" t="s">
-        <x:v>530</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>531</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>532</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="D10" s="6" t="s">
-        <x:v>533</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -8067,7 +7965,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="20" t="s">
-        <x:v>534</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B12" s="20"/>
       <x:c r="C12" s="20"/>
@@ -8075,72 +7973,72 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>515</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="6" t="s">
-        <x:v>153</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>539</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>540</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D14" s="6" t="s">
-        <x:v>541</x:v>
+        <x:v>518</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>542</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>543</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="D15" s="6" t="s">
-        <x:v>544</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="6" t="s">
-        <x:v>161</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>545</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
-        <x:v>546</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="D16" s="6" t="s">
-        <x:v>547</x:v>
+        <x:v>524</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="6" t="s">
-        <x:v>164</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>548</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="C17" s="6" t="s">
-        <x:v>546</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="D17" s="6" t="s">
-        <x:v>549</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8151,7 +8049,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="20" t="s">
-        <x:v>550</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B19" s="20"/>
       <x:c r="C19" s="20"/>
@@ -8159,114 +8057,114 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>425</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="6" t="s">
-        <x:v>554</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B21" s="6" t="s">
-        <x:v>555</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="C21" s="6" t="s">
-        <x:v>556</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="D21" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="6" t="s">
-        <x:v>557</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B22" s="6" t="s">
-        <x:v>558</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="C22" s="6" t="s">
-        <x:v>559</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D22" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="6" t="s">
-        <x:v>560</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B23" s="6" t="s">
-        <x:v>561</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="C23" s="6" t="s">
-        <x:v>562</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="D23" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="6" t="s">
-        <x:v>563</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B24" s="6" t="s">
-        <x:v>564</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="C24" s="6" t="s">
-        <x:v>565</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D24" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="6" t="s">
-        <x:v>566</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B25" s="6" t="s">
-        <x:v>567</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C25" s="6" t="s">
-        <x:v>568</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D25" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="6" t="s">
-        <x:v>569</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B26" s="6" t="s">
-        <x:v>570</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C26" s="6" t="s">
-        <x:v>571</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="D26" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="26">
       <x:c r="A27" s="6" t="s">
-        <x:v>572</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B27" s="6" t="s">
-        <x:v>573</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="C27" s="6" t="s">
-        <x:v>574</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D27" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -8277,7 +8175,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="20" t="s">
-        <x:v>575</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B29" s="20"/>
       <x:c r="C29" s="20"/>
@@ -8285,114 +8183,114 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="3" t="s">
-        <x:v>468</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>425</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="6" t="s">
-        <x:v>470</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B31" s="6" t="s">
-        <x:v>578</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="C31" s="6" t="s">
-        <x:v>579</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D31" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="6" t="s">
-        <x:v>472</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B32" s="6" t="s">
-        <x:v>580</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C32" s="6" t="s">
-        <x:v>581</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="D32" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="6" t="s">
-        <x:v>474</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B33" s="6" t="s">
-        <x:v>582</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="C33" s="6" t="s">
-        <x:v>581</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="D33" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="6" t="s">
-        <x:v>476</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B34" s="6" t="s">
-        <x:v>583</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C34" s="6" t="s">
-        <x:v>584</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D34" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="6" t="s">
-        <x:v>478</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B35" s="6" t="s">
-        <x:v>585</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="C35" s="6" t="s">
-        <x:v>586</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D35" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="6" t="s">
-        <x:v>587</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B36" s="6" t="s">
-        <x:v>164</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C36" s="6" t="s">
-        <x:v>588</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D36" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="6" t="s">
-        <x:v>589</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B37" s="6" t="s">
-        <x:v>590</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="C37" s="6" t="s">
-        <x:v>591</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="D37" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -8403,7 +8301,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="20" t="s">
-        <x:v>592</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B39" s="20"/>
       <x:c r="C39" s="20"/>
@@ -8414,10 +8312,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B40" s="6" t="s">
-        <x:v>593</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="C40" s="6" t="s">
-        <x:v>594</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D40" s="6"/>
     </x:row>
@@ -8426,10 +8324,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B41" s="6" t="s">
-        <x:v>595</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C41" s="6" t="s">
-        <x:v>596</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="D41" s="6"/>
     </x:row>
@@ -8438,10 +8336,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B42" s="6" t="s">
-        <x:v>597</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="C42" s="6" t="s">
-        <x:v>598</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D42" s="6"/>
     </x:row>
@@ -8450,10 +8348,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B43" s="6" t="s">
-        <x:v>599</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="C43" s="6" t="s">
-        <x:v>600</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="D43" s="6"/>
     </x:row>
@@ -8462,10 +8360,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B44" s="6" t="s">
-        <x:v>601</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="C44" s="6" t="s">
-        <x:v>602</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D44" s="6"/>
     </x:row>
@@ -8474,10 +8372,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B45" s="6" t="s">
-        <x:v>603</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="C45" s="6" t="s">
-        <x:v>604</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="D45" s="6"/>
     </x:row>
@@ -8486,10 +8384,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="6" t="s">
-        <x:v>605</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="C46" s="6" t="s">
-        <x:v>606</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="D46" s="6"/>
     </x:row>
@@ -8498,10 +8396,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B47" s="6" t="s">
-        <x:v>607</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="C47" s="6" t="s">
-        <x:v>608</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="D47" s="6"/>
     </x:row>
@@ -8510,10 +8408,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B48" s="6" t="s">
-        <x:v>609</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="C48" s="6" t="s">
-        <x:v>610</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="D48" s="6"/>
     </x:row>
@@ -8525,7 +8423,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="20" t="s">
-        <x:v>611</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B50" s="20"/>
       <x:c r="C50" s="20"/>
@@ -8539,7 +8437,7 @@
         <x:v>Use ConveyorControllerCD:11009 and RotaryTableControllerCD:11003 as the separate status receivers.</x:v>
       </x:c>
       <x:c r="C51" s="25" t="str">
-        <x:v>M1 production XML is aligned; real M2/M3 peer source/XML remains unavailable.</x:v>
+        <x:v>M1 and M3 production XML is aligned; M2 Conveyor peer remains unavailable.</x:v>
       </x:c>
       <x:c r="D51" s="25" t="str">
         <x:v>M1 + M2 + M3 integration</x:v>
@@ -8547,16 +8445,16 @@
     </x:row>
     <x:row r="52" ht="26">
       <x:c r="A52" s="11" t="s">
-        <x:v>612</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B52" s="11">
         <x:v>13002</x:v>
       </x:c>
       <x:c r="C52" s="11" t="s">
-        <x:v>613</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="D52" s="11" t="s">
-        <x:v>614</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -8567,24 +8465,24 @@
         <x:v>V2.1 receiver is RotaryTableControllerCD:11003</x:v>
       </x:c>
       <x:c r="C53" s="8" t="str">
-        <x:v>Current M1 production XML matches; actual M3 source/XML unavailable</x:v>
+        <x:v>Current M1 production XML and M3 RotaryTableControllerCD:11003 implementation match.</x:v>
       </x:c>
       <x:c r="D53" s="8" t="str">
-        <x:v>M3 implementation verification</x:v>
+        <x:v>M3 implemented; merged M2 pipeline still pending</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="8" t="s">
-        <x:v>615</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B54" s="8" t="s">
-        <x:v>616</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="C54" s="8" t="s">
-        <x:v>617</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="D54" s="8" t="s">
-        <x:v>618</x:v>
+        <x:v>595</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8612,7 +8510,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="19" t="s">
-        <x:v>619</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -8624,13 +8522,13 @@
     </x:row>
     <x:row r="3" ht="14" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>425</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="14" customHeight="1">
@@ -8638,7 +8536,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>5</x:v>
@@ -8649,7 +8547,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>623</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>5</x:v>
@@ -8660,7 +8558,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>5</x:v>
@@ -8671,7 +8569,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>625</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>5</x:v>
@@ -8682,7 +8580,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>626</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>5</x:v>
@@ -8695,19 +8593,19 @@
     </x:row>
     <x:row r="10" ht="14" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>627</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>628</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C10" s="1"/>
     </x:row>
     <x:row r="11" ht="14" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>629</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="C11" s="1"/>
     </x:row>
@@ -8733,36 +8631,36 @@
   <x:sheetData>
     <x:row r="1" ht="28">
       <x:c r="A1" s="49" t="s">
-        <x:v>631</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B1" s="49" t="s">
-        <x:v>632</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="C1" s="49" t="s">
-        <x:v>633</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D1" s="49" t="s">
-        <x:v>634</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="E1" s="49" t="s">
-        <x:v>635</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="F1" s="49" t="s">
-        <x:v>636</x:v>
+        <x:v>613</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="50" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B2" s="50" t="s">
-        <x:v>529</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="C2" s="50">
         <x:v>11009</x:v>
       </x:c>
       <x:c r="D2" s="50" t="s">
-        <x:v>637</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="E2" s="50" t="str">
         <x:v>PASS AT M1 — PRODUCTION MAPPING ALIGNED</x:v>
@@ -8785,27 +8683,27 @@
         <x:v>M1 V1 + M3 V2.1 + M4 V1.2</x:v>
       </x:c>
       <x:c r="E3" s="50" t="str">
-        <x:v>PASS AT M1 — FROZEN RECEIVER ALIGNED</x:v>
+        <x:v>PASS — M1/M3 FROZEN RECEIVER AND FULL-CONTEXT PATH IMPLEMENTED</x:v>
       </x:c>
       <x:c r="F3" s="50" t="str">
-        <x:v>Verify real M3 Rotary source/XML; separate M4 payload approval remains open</x:v>
+        <x:v>Retain current XML and verify the final merged M2 pipeline</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="28">
       <x:c r="A4" s="50" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B4" s="50" t="s">
-        <x:v>529</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="C4" s="50">
         <x:v>11013</x:v>
       </x:c>
       <x:c r="D4" s="50" t="s">
-        <x:v>638</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="E4" s="50" t="s">
-        <x:v>639</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="F4" s="50" t="str">
         <x:v>M3 maps BOTTLE_AT_LABEL; Coordinator status polling remains proposed pending team acceptance</x:v>
@@ -8813,196 +8711,196 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="50" t="s">
-        <x:v>348</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B5" s="50" t="s">
-        <x:v>640</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="C5" s="50">
         <x:v>11011</x:v>
       </x:c>
       <x:c r="D5" s="50" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="E5" s="50" t="s">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="F5" s="50" t="s">
-        <x:v>643</x:v>
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="E5" s="50" t="str">
+        <x:v>PASS — M4 IMPLEMENTED AT 11011</x:v>
+      </x:c>
+      <x:c r="F5" s="50" t="str">
+        <x:v>M4 model/SystemJ tests pass; M2 profile peers remain pending</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="50" t="s">
-        <x:v>253</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B6" s="50" t="s">
-        <x:v>640</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="C6" s="50">
         <x:v>11012</x:v>
       </x:c>
       <x:c r="D6" s="50" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="E6" s="50" t="s">
-        <x:v>644</x:v>
-      </x:c>
-      <x:c r="F6" s="50" t="s">
-        <x:v>643</x:v>
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="E6" s="50" t="str">
+        <x:v>PASS — M4 IMPLEMENTED AT 11012</x:v>
+      </x:c>
+      <x:c r="F6" s="50" t="str">
+        <x:v>M4 SortPack path passes; verify M2 Unloader sender when available</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="50" t="s">
-        <x:v>280</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B7" s="50" t="s">
-        <x:v>529</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="C7" s="50">
         <x:v>12013</x:v>
       </x:c>
       <x:c r="D7" s="50" t="s">
-        <x:v>638</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="E7" s="50" t="s">
-        <x:v>645</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="F7" s="50" t="s">
-        <x:v>646</x:v>
+        <x:v>620</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28">
       <x:c r="A8" s="50" t="s">
-        <x:v>647</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="B8" s="50" t="s">
-        <x:v>640</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="C8" s="50" t="s">
-        <x:v>648</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="D8" s="50" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="E8" s="50" t="s">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="F8" s="50" t="s">
-        <x:v>643</x:v>
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="E8" s="50" t="str">
+        <x:v>PASS — M4 PLANTS IMPLEMENTED AT 12011 / 12012</x:v>
+      </x:c>
+      <x:c r="F8" s="50" t="str">
+        <x:v>Covered by M4 model and SystemJ demo</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="50" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B9" s="50" t="s">
-        <x:v>529</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="C9" s="50">
         <x:v>13002</x:v>
       </x:c>
       <x:c r="D9" s="50" t="s">
-        <x:v>637</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="E9" s="50" t="s">
-        <x:v>649</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="F9" s="50" t="s">
-        <x:v>650</x:v>
+        <x:v>624</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="50" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B10" s="50" t="s">
-        <x:v>526</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="C10" s="50">
         <x:v>13003</x:v>
       </x:c>
       <x:c r="D10" s="50" t="s">
-        <x:v>651</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="E10" s="50" t="s">
-        <x:v>652</x:v>
-      </x:c>
-      <x:c r="F10" s="50" t="s">
-        <x:v>653</x:v>
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="F10" s="50" t="str">
+        <x:v>M3 implementation present; full M2/M3 fault test remains pending</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28">
       <x:c r="A11" s="50" t="s">
-        <x:v>298</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B11" s="50" t="s">
-        <x:v>654</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="C11" s="50">
         <x:v>14002</x:v>
       </x:c>
       <x:c r="D11" s="50" t="s">
-        <x:v>638</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="E11" s="50" t="s">
-        <x:v>655</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="F11" s="50" t="s">
-        <x:v>656</x:v>
+        <x:v>629</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28">
       <x:c r="A12" s="50" t="s">
-        <x:v>510</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B12" s="50" t="s">
-        <x:v>657</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="C12" s="50" t="s">
-        <x:v>658</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="D12" s="50" t="s">
-        <x:v>659</x:v>
-      </x:c>
-      <x:c r="E12" s="50" t="s">
-        <x:v>660</x:v>
-      </x:c>
-      <x:c r="F12" s="50" t="s">
-        <x:v>661</x:v>
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="E12" s="50" t="str">
+        <x:v>M4 SENDER IMPLEMENTED; M2 RECEIVERS PENDING</x:v>
+      </x:c>
+      <x:c r="F12" s="50" t="str">
+        <x:v>Verify M2 validation and unchanged forwarding when its implementation arrives</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="28">
       <x:c r="A13" s="50" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B13" s="50" t="s">
-        <x:v>662</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="C13" s="50">
         <x:v>11012</x:v>
       </x:c>
       <x:c r="D13" s="50" t="s">
-        <x:v>659</x:v>
-      </x:c>
-      <x:c r="E13" s="50" t="s">
-        <x:v>663</x:v>
-      </x:c>
-      <x:c r="F13" s="50" t="s">
-        <x:v>664</x:v>
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="E13" s="50" t="str">
+        <x:v>M4 RECEIVER IMPLEMENTED; M2 SENDER PENDING</x:v>
+      </x:c>
+      <x:c r="F13" s="50" t="str">
+        <x:v>Verify merged M2 Unloader-to-M4 SortPack hand-off</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="28">
       <x:c r="A14" s="50" t="s">
-        <x:v>665</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="B14" s="50" t="s">
-        <x:v>666</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="C14" s="50" t="s">
-        <x:v>667</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D14" s="50" t="s">
-        <x:v>638</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="E14" s="50" t="str">
         <x:v>PROPOSED — NOT IMPLEMENTED IN M1</x:v>
@@ -9025,10 +8923,10 @@
         <x:v>M1 V1 + M4 V1.2</x:v>
       </x:c>
       <x:c r="E15" s="54" t="str">
-        <x:v>PASS — CURRENT M1 VALIDATION ENFORCES INVARIANT</x:v>
+        <x:v>PASS — M1 VALIDATION AND M4 CONTROLLERS IMPLEMENTED</x:v>
       </x:c>
       <x:c r="F15" s="54" t="str">
-        <x:v>No M1 code change; retain OrderV1 validation and verify with real M4 Controllers</x:v>
+        <x:v>Covered by OrderV1 and Member4ModelSelfTest</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
@@ -9045,10 +8943,10 @@
         <x:v>M4 V1.2</x:v>
       </x:c>
       <x:c r="E16" s="54" t="str">
-        <x:v>PORT/NAME RESOLVED; M4-TO-M3 PAYLOAD PROPOSED</x:v>
+        <x:v>PASS — M4/M3 FULL-CONTEXT PATH IMPLEMENTED</x:v>
       </x:c>
       <x:c r="F16" s="54" t="str">
-        <x:v>M3 approves full BottleContext and implements the receiver; no Coordinator declaration required</x:v>
+        <x:v>No Coordinator declaration; retain exact payload and port</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
@@ -9065,10 +8963,10 @@
         <x:v>M4 V1.2</x:v>
       </x:c>
       <x:c r="E17" s="54" t="str">
-        <x:v>PROPOSED — M3 payload approval required</x:v>
+        <x:v>PASS — M3/M4 SAME-BOTTLE P2/P4 RELAYS IMPLEMENTED</x:v>
       </x:c>
       <x:c r="F17" s="54" t="str">
-        <x:v>Approve full BottleContext and implement same-bottle P2/P4 relay</x:v>
+        <x:v>Covered by Member3Member4IntegrationSelfTest and the M4 two-size SystemJ demo</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
@@ -9085,10 +8983,10 @@
         <x:v>M3 V2.1 + M4 V1.2</x:v>
       </x:c>
       <x:c r="E18" s="54" t="str">
-        <x:v>PASS — frozen M3 Plant receiver retained</x:v>
+        <x:v>PASS — M4 SENDERS AND M3 PLANT RECEIVER IMPLEMENTED</x:v>
       </x:c>
       <x:c r="F18" s="54" t="str">
-        <x:v>Implement exactly-once bottle-correlated sends</x:v>
+        <x:v>Retain bottle correlation and idempotent bounded transport</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
@@ -9164,270 +9062,270 @@
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="57" t="s">
-        <x:v>668</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="B4" s="57" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C4" s="57" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D4" s="57" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C4" s="57" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D4" s="57" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="E4" s="57" t="s">
-        <x:v>669</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="F4" s="57" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G4" s="57" t="s">
-        <x:v>670</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="H4" s="57" t="s">
-        <x:v>671</x:v>
+        <x:v>640</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26">
       <x:c r="A5" s="28" t="s">
-        <x:v>672</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="B5" s="28" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C5" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D5" s="28" t="s">
-        <x:v>175</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E5" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F5" s="28">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="G5" s="28" t="s">
-        <x:v>673</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="H5" s="28" t="s">
-        <x:v>674</x:v>
+        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="27" t="s">
-        <x:v>675</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>181</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C6" s="27" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D6" s="27" t="s">
-        <x:v>182</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E6" s="27" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F6" s="27">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="G6" s="27" t="s">
-        <x:v>676</x:v>
-      </x:c>
-      <x:c r="H6" s="27" t="s">
-        <x:v>677</x:v>
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="H6" s="27" t="str">
+        <x:v>FROZEN; implemented at M4 sender and M3 receiver</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="27" t="s">
-        <x:v>678</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="B7" s="27" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C7" s="27" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D7" s="27" t="s">
-        <x:v>188</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E7" s="27" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F7" s="27" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G7" s="27" t="s">
-        <x:v>679</x:v>
-      </x:c>
-      <x:c r="H7" s="27" t="s">
-        <x:v>680</x:v>
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="H7" s="27" t="str">
+        <x:v>FROZEN; implemented within M3</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="27" t="s">
-        <x:v>678</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="B8" s="27" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C8" s="27" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D8" s="27" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D8" s="27" t="s">
-        <x:v>192</x:v>
-      </x:c>
       <x:c r="E8" s="27" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F8" s="27" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G8" s="27" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="H8" s="27" t="s">
-        <x:v>680</x:v>
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="H8" s="27" t="str">
+        <x:v>FROZEN; implemented within M3</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="27" t="s">
-        <x:v>682</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="B9" s="27" t="s">
-        <x:v>195</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C9" s="27" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D9" s="27" t="s">
-        <x:v>196</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E9" s="27" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F9" s="27">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="G9" s="27" t="s">
-        <x:v>683</x:v>
-      </x:c>
-      <x:c r="H9" s="27" t="s">
-        <x:v>677</x:v>
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="H9" s="27" t="str">
+        <x:v>FROZEN; implemented at M4 sender and M3 receiver</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26">
       <x:c r="A10" s="28" t="s">
-        <x:v>684</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B10" s="28" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C10" s="28" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D10" s="28" t="s">
-        <x:v>200</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E10" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F10" s="25">
         <x:v>11013</x:v>
       </x:c>
       <x:c r="G10" s="25" t="s">
-        <x:v>685</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="H10" s="25" t="s">
-        <x:v>686</x:v>
+        <x:v>653</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26">
       <x:c r="A11" s="28" t="s">
-        <x:v>684</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B11" s="28" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C11" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D11" s="28" t="s">
-        <x:v>204</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E11" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F11" s="28">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="G11" s="28" t="s">
-        <x:v>687</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="H11" s="28" t="s">
-        <x:v>674</x:v>
+        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="26">
       <x:c r="A12" s="28" t="s">
-        <x:v>684</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B12" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C12" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D12" s="28" t="s">
-        <x:v>208</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E12" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F12" s="28">
         <x:v>12003</x:v>
       </x:c>
       <x:c r="G12" s="28" t="s">
-        <x:v>688</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="H12" s="28" t="s">
-        <x:v>674</x:v>
+        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26">
       <x:c r="A13" s="28" t="s">
-        <x:v>689</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B13" s="28" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C13" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D13" s="28" t="s">
-        <x:v>248</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E13" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F13" s="28">
         <x:v>11010</x:v>
       </x:c>
       <x:c r="G13" s="28" t="s">
-        <x:v>690</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="H13" s="28" t="s">
-        <x:v>691</x:v>
+        <x:v>658</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="58" t="s">
-        <x:v>692</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="B14" s="58" t="s">
-        <x:v>693</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="C14" s="58"/>
       <x:c r="D14" s="58"/>
@@ -9438,10 +9336,10 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="58" t="s">
-        <x:v>694</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="B15" s="58" t="s">
-        <x:v>695</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="C15" s="58"/>
       <x:c r="D15" s="58"/>
@@ -9452,28 +9350,28 @@
     </x:row>
     <x:row r="16" ht="26">
       <x:c r="A16" s="28" t="s">
-        <x:v>696</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="B16" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C16" s="28" t="s">
-        <x:v>253</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D16" s="28" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E16" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F16" s="28">
         <x:v>11012</x:v>
       </x:c>
       <x:c r="G16" s="28" t="s">
-        <x:v>697</x:v>
-      </x:c>
-      <x:c r="H16" s="28" t="s">
-        <x:v>698</x:v>
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="H16" s="28" t="str">
+        <x:v>M4 receiver/Plant implemented; M2 Unloader sender pending</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -9499,7 +9397,7 @@
         <x:v>Create once for a new valid bottleId; reject unknown size/capacity mismatch</x:v>
       </x:c>
       <x:c r="H17" s="36" t="str">
-        <x:v>M4 V1.2 proposed</x:v>
+        <x:v>M4 V1.2 implemented</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -9522,10 +9420,10 @@
         <x:v>11003</x:v>
       </x:c>
       <x:c r="G18" s="36" t="str">
-        <x:v>M3 payload approval and implementation required; not an M1 Coordinator signal</x:v>
+        <x:v>Forward the unchanged validated full context; not an M1 Coordinator signal</x:v>
       </x:c>
       <x:c r="H18" s="36" t="str">
-        <x:v>M4 V1.2 proposed; M1 receiver mapping no longer blocks the peer hand-off</x:v>
+        <x:v>Implemented at M4 Registry sender and M3 Rotary receiver</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -9551,7 +9449,7 @@
         <x:v>Same bottleId physically confirmed at Position 2</x:v>
       </x:c>
       <x:c r="H19" s="36" t="str">
-        <x:v>M4 V1.2 proposed; M3 approval required</x:v>
+        <x:v>Implemented at M3 sender and M4 Filler A receiver</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -9577,7 +9475,7 @@
         <x:v>All A outputs safe; matching context; measured A acceptable</x:v>
       </x:c>
       <x:c r="H20" s="36" t="str">
-        <x:v>M4-internal proposed hand-off</x:v>
+        <x:v>Implemented M4-internal idempotent hand-off</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -9603,7 +9501,7 @@
         <x:v>Same bottleId physically confirmed at Position 4</x:v>
       </x:c>
       <x:c r="H21" s="36" t="str">
-        <x:v>M4 V1.2 proposed; M3 approval required</x:v>
+        <x:v>Implemented at M3 sender and M4 Capper receiver</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9629,7 +9527,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="61" t="str">
-        <x:v>M4 V1.2 — Integration Acceptance and Freeze Gates</x:v>
+        <x:v>M4 V1.2 — Implementation Verification</x:v>
       </x:c>
       <x:c r="B1" s="61"/>
       <x:c r="C1" s="61"/>
@@ -9637,7 +9535,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="64" t="str">
-        <x:v>Source: COMPSYS704_M4_GP_IP_Integration_Interface_Contract_V1_2.docx | Proposed for team freeze</x:v>
+        <x:v>Source: COMPSYS704_M4_GP_IP_Integration_Interface_Contract_V1_2.docx | Implementation sync: 2 September 2026</x:v>
       </x:c>
       <x:c r="B2" s="64"/>
       <x:c r="C2" s="64"/>
@@ -9645,7 +9543,7 @@
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" s="117" t="str">
-        <x:v>Open gates: M3 approval/implementation of ROTARY_BOTTLE_CONTEXT, BOTTLE_AT_FILL and BOTTLE_AT_CAP; merged-XML verification; promote the workbook target-volume and bottleId clarifications into the next M4 contract revision. M1 mapping and recipe-pair validation are confirmed; M2 profile/sort payload approval is recorded.</x:v>
+        <x:v>M4 local implementation gates are complete: production XML is registered, deterministic model tests pass, and the two-size SystemJ demo passes. Remaining cross-member work is limited to pending M2 profile and downstream SortPack peer endpoints.</x:v>
       </x:c>
       <x:c r="B3" s="117"/>
       <x:c r="C3" s="117"/>
@@ -9677,7 +9575,7 @@
         <x:v>No M4 operation starts, advances, resets or acknowledges.</x:v>
       </x:c>
       <x:c r="D6" s="75" t="str">
-        <x:v>M1/M4 integration</x:v>
+        <x:v>PASS — read-only polling implemented</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
@@ -9691,7 +9589,7 @@
         <x:v>120 mL A + 80 mL B; GEOM_S set-points; PACK_S lane/package; exactly-once completion.</x:v>
       </x:c>
       <x:c r="D7" s="76" t="str">
-        <x:v>M4</x:v>
+        <x:v>PASS — model test and SystemJ demo</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
@@ -9705,7 +9603,7 @@
         <x:v>300 mL A + 200 mL B; GEOM_L set-points; PACK_L lane/package; exactly-once completion.</x:v>
       </x:c>
       <x:c r="D8" s="75" t="str">
-        <x:v>M4</x:v>
+        <x:v>PASS — model test and SystemJ demo</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
@@ -9719,7 +9617,7 @@
         <x:v>Unknown/local-invalid input starts no actuator. M1 rejects a non-100-sum pair before dispatch; forced complement mismatch keeps Filler B closed and reports FAULT.</x:v>
       </x:c>
       <x:c r="D9" s="76" t="str">
-        <x:v>M1 + M4</x:v>
+        <x:v>PASS — M1 validation and M4 fault test</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
@@ -9733,7 +9631,7 @@
         <x:v>Filler B starts only after one matching safe completion; stale/duplicate messages do no work.</x:v>
       </x:c>
       <x:c r="D10" s="75" t="str">
-        <x:v>M4</x:v>
+        <x:v>PASS — identity/gating test</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
@@ -9747,7 +9645,7 @@
         <x:v>Outputs de-energise; no false FILL_A_DONE, MARK_FILLED or MARK_CAPPED.</x:v>
       </x:c>
       <x:c r="D11" s="76" t="str">
-        <x:v>M4</x:v>
+        <x:v>PASS — safe-state fault tests</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
@@ -9761,7 +9659,7 @@
         <x:v>Correct grip/clamp set-points; one guarded sequence; no duplicate restart.</x:v>
       </x:c>
       <x:c r="D12" s="75" t="str">
-        <x:v>M4</x:v>
+        <x:v>PASS — S/L geometry and idempotency test</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
@@ -9775,7 +9673,7 @@
         <x:v>Unchanged full BottleContext reaches 11012; expected lane and placement are confirmed before count; BOTTLE_DONE remains M2-owned.</x:v>
       </x:c>
       <x:c r="D13" s="76" t="str">
-        <x:v>M2 + M4; M2 approval recorded</x:v>
+        <x:v>M4 PASS; merged M2 sender test pending</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1"/>
@@ -9809,7 +9707,7 @@
         <x:v>Retain frozen ratio/status ports and M2-only BOTTLE_DONE; M1 recipe-pair validation and Conveyor/Rotary sender mappings are confirmed.</x:v>
       </x:c>
       <x:c r="C17" s="48" t="str">
-        <x:v>COMPLETE AT M1 / PEER UNVERIFIED</x:v>
+        <x:v>COMPLETE AT M1; M2 PEERS PENDING</x:v>
       </x:c>
       <x:c r="D17" s="48" t="str">
         <x:v>Current M1 source/XML, OrderV1SelfTest and integration regression</x:v>
@@ -9823,7 +9721,7 @@
         <x:v>Preserve full context for LOAD_PROFILE, UNLOAD_PROFILE and BOTTLE_READY_FOR_SORT; retain BOTTLE_DONE ownership.</x:v>
       </x:c>
       <x:c r="C18" s="48" t="str">
-        <x:v>APPROVED IN MASTER WORKBOOK</x:v>
+        <x:v>PAYLOAD APPROVED; M2 IMPLEMENTATION PENDING</x:v>
       </x:c>
       <x:c r="D18" s="48" t="str">
         <x:v>Implementation and integration-test evidence</x:v>
@@ -9837,10 +9735,10 @@
         <x:v>Reconcile Rotary Controller with M1; approve ROTARY_BOTTLE_CONTEXT, BOTTLE_AT_FILL and BOTTLE_AT_CAP; retain Plant 12003.</x:v>
       </x:c>
       <x:c r="C19" s="48" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>COMPLETE AT M3/M4 BOUNDARY</x:v>
       </x:c>
       <x:c r="D19" s="48" t="str">
-        <x:v>Written receiver/payload reply</x:v>
+        <x:v>Current M3 source/XML and interface validator</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="60" customHeight="1">
@@ -9851,10 +9749,10 @@
         <x:v>Implement Registry, Filler A/B, Capper and SortPack on assigned ports; publish target-volume and bottleId clarifications in the next contract revision; verify merged XML; execute T1-T8.</x:v>
       </x:c>
       <x:c r="C20" s="118" t="str">
-        <x:v>PROPOSED — CLARIFICATIONS RECORDED</x:v>
+        <x:v>IMPLEMENTED AND VERIFIED</x:v>
       </x:c>
       <x:c r="D20" s="118" t="str">
-        <x:v>Merged XML and passing tests</x:v>
+        <x:v>Member4ModelSelfTest PASSED; Member3Member4IntegrationSelfTest PASSED; two-size SystemJ demo PASSED; production XML registered</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="28" customHeight="1"/>
@@ -9868,7 +9766,7 @@
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
       <x:c r="A23" s="98" t="str">
-        <x:v>Integration is complete when real peer SystemJ/XML is verified; M3 approves and implements the proposed BottleContext hand-offs; approved signals compile without port conflict; each S/L bottle retains one validated context; Filler B starts only after matching safe FILL_A_DONE; faults enter a safe state; MARK_FILLED and MARK_CAPPED reach RotaryTablePlantCD:12003 exactly once; only M2 emits BOTTLE_DONE; SortPack never advances POS; and T1-T8 pass. M1 status mappings and the recipe-pair invariant are already aligned.</x:v>
+        <x:v>M4 local definition of done is satisfied: S/L bottles retain one validated context; Filler B is gated by matching safe FILL_A_DONE; faults enter a safe state; MARK_FILLED and MARK_CAPPED reach RotaryTablePlantCD:12003 without M4 claiming BOTTLE_DONE; SortPack verifies lane and placement before counting. Full group end-to-end completion still requires the pending M2 Loader/Conveyor/Labeller/Unloader and Transfer Adapter endpoints.</x:v>
       </x:c>
       <x:c r="B23" s="99"/>
       <x:c r="C23" s="99"/>
